--- a/database/event/8045/event_8045_evp_summary.xlsx
+++ b/database/event/8045/event_8045_evp_summary.xlsx
@@ -499,7 +499,7 @@
         <v>11.5103</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>4.5742</v>
       </c>
       <c r="D2" t="n">
         <v>4.2285</v>
@@ -545,7 +545,7 @@
         <v>7.8219</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>3.1085</v>
       </c>
       <c r="D3" t="n">
         <v>2.7385</v>
@@ -591,7 +591,7 @@
         <v>6.9795</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>2.7737</v>
       </c>
       <c r="D4" t="n">
         <v>2.3982</v>
@@ -637,7 +637,7 @@
         <v>6.7354</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>2.6767</v>
       </c>
       <c r="D5" t="n">
         <v>2.2996</v>
@@ -683,7 +683,7 @@
         <v>6.0511</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>2.4047</v>
       </c>
       <c r="D6" t="n">
         <v>2.0231</v>
@@ -729,7 +729,7 @@
         <v>5.9345</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>2.3584</v>
       </c>
       <c r="D7" t="n">
         <v>1.976</v>
@@ -775,7 +775,7 @@
         <v>5.7447</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>2.283</v>
       </c>
       <c r="D8" t="n">
         <v>1.8994</v>
@@ -821,7 +821,7 @@
         <v>5.5098</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>2.1896</v>
       </c>
       <c r="D9" t="n">
         <v>1.8045</v>
@@ -867,7 +867,7 @@
         <v>5.4963</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>2.1843</v>
       </c>
       <c r="D10" t="n">
         <v>1.799</v>
@@ -913,7 +913,7 @@
         <v>5.4263</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>2.1564</v>
       </c>
       <c r="D11" t="n">
         <v>1.7707</v>
@@ -959,7 +959,7 @@
         <v>5.0263</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>1.9975</v>
       </c>
       <c r="D12" t="n">
         <v>1.6092</v>
@@ -1005,7 +1005,7 @@
         <v>4.8084</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>1.9109</v>
       </c>
       <c r="D13" t="n">
         <v>1.5211</v>
@@ -1051,7 +1051,7 @@
         <v>4.4055</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>1.7508</v>
       </c>
       <c r="D14" t="n">
         <v>1.3584</v>
@@ -1097,7 +1097,7 @@
         <v>4.2076</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>1.6721</v>
       </c>
       <c r="D15" t="n">
         <v>1.2784</v>
@@ -1143,7 +1143,7 @@
         <v>3.9373</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>1.5647</v>
       </c>
       <c r="D16" t="n">
         <v>1.1692</v>
@@ -1189,7 +1189,7 @@
         <v>3.7229</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1.4795</v>
       </c>
       <c r="D17" t="n">
         <v>1.0826</v>
@@ -1235,7 +1235,7 @@
         <v>3.6072</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>1.4335</v>
       </c>
       <c r="D18" t="n">
         <v>1.0359</v>
@@ -1281,7 +1281,7 @@
         <v>3.576</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>1.4211</v>
       </c>
       <c r="D19" t="n">
         <v>1.0233</v>
@@ -1327,7 +1327,7 @@
         <v>3.3353</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>1.3255</v>
       </c>
       <c r="D20" t="n">
         <v>0.926</v>
@@ -1373,7 +1373,7 @@
         <v>3.2565</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>1.2941</v>
       </c>
       <c r="D21" t="n">
         <v>0.8942</v>
@@ -1419,7 +1419,7 @@
         <v>3.1025</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>1.2329</v>
       </c>
       <c r="D22" t="n">
         <v>0.832</v>
@@ -1465,7 +1465,7 @@
         <v>2.9998</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>1.1921</v>
       </c>
       <c r="D23" t="n">
         <v>0.7905</v>
@@ -1511,7 +1511,7 @@
         <v>2.8508</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>1.1329</v>
       </c>
       <c r="D24" t="n">
         <v>0.7302999999999999</v>
@@ -1557,7 +1557,7 @@
         <v>2.7503</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>1.093</v>
       </c>
       <c r="D25" t="n">
         <v>0.6897</v>
@@ -1603,7 +1603,7 @@
         <v>2.7456</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>1.0911</v>
       </c>
       <c r="D26" t="n">
         <v>0.6878</v>
@@ -1649,7 +1649,7 @@
         <v>2.6075</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>1.0362</v>
       </c>
       <c r="D27" t="n">
         <v>0.632</v>
@@ -1695,7 +1695,7 @@
         <v>2.512</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>0.9983</v>
       </c>
       <c r="D28" t="n">
         <v>0.5934</v>
@@ -1741,7 +1741,7 @@
         <v>2.045</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>0.8127</v>
       </c>
       <c r="D29" t="n">
         <v>0.4048</v>
@@ -1787,7 +1787,7 @@
         <v>1.9653</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>0.781</v>
       </c>
       <c r="D30" t="n">
         <v>0.3726</v>
@@ -1833,7 +1833,7 @@
         <v>1.824</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>0.7249</v>
       </c>
       <c r="D31" t="n">
         <v>0.3155</v>
@@ -1879,7 +1879,7 @@
         <v>1.7481</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>0.6947</v>
       </c>
       <c r="D32" t="n">
         <v>0.2848</v>
@@ -1925,7 +1925,7 @@
         <v>1.7272</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>0.6864</v>
       </c>
       <c r="D33" t="n">
         <v>0.2764</v>
@@ -1971,7 +1971,7 @@
         <v>1.7216</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>0.6842</v>
       </c>
       <c r="D34" t="n">
         <v>0.2741</v>
@@ -2017,7 +2017,7 @@
         <v>1.6577</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>0.6588000000000001</v>
       </c>
       <c r="D35" t="n">
         <v>0.2483</v>
@@ -2063,7 +2063,7 @@
         <v>1.6041</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>0.6375</v>
       </c>
       <c r="D36" t="n">
         <v>0.2267</v>
@@ -2109,7 +2109,7 @@
         <v>1.4867</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>0.5908</v>
       </c>
       <c r="D37" t="n">
         <v>0.1792</v>
@@ -2155,7 +2155,7 @@
         <v>1.1484</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>0.4564</v>
       </c>
       <c r="D38" t="n">
         <v>0.0426</v>
@@ -2201,7 +2201,7 @@
         <v>1.0385</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>0.4127</v>
       </c>
       <c r="D39" t="n">
         <v>-0.0018</v>
@@ -2247,7 +2247,7 @@
         <v>0.9902</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>0.3935</v>
       </c>
       <c r="D40" t="n">
         <v>-0.0213</v>
@@ -2293,7 +2293,7 @@
         <v>0.9189000000000001</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>0.3652</v>
       </c>
       <c r="D41" t="n">
         <v>-0.0501</v>
@@ -2339,7 +2339,7 @@
         <v>0.8554</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>0.3399</v>
       </c>
       <c r="D42" t="n">
         <v>-0.07580000000000001</v>
@@ -2385,7 +2385,7 @@
         <v>0.8082</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>0.3212</v>
       </c>
       <c r="D43" t="n">
         <v>-0.0949</v>
@@ -2431,7 +2431,7 @@
         <v>0.7408</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>0.2944</v>
       </c>
       <c r="D44" t="n">
         <v>-0.1221</v>
@@ -2477,7 +2477,7 @@
         <v>0.7317</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>0.2908</v>
       </c>
       <c r="D45" t="n">
         <v>-0.1258</v>
@@ -2523,7 +2523,7 @@
         <v>0.5693</v>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>0.2262</v>
       </c>
       <c r="D46" t="n">
         <v>-0.1914</v>
@@ -2569,7 +2569,7 @@
         <v>0.5508</v>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>0.2189</v>
       </c>
       <c r="D47" t="n">
         <v>-0.1989</v>
@@ -2615,7 +2615,7 @@
         <v>0.5184</v>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>0.206</v>
       </c>
       <c r="D48" t="n">
         <v>-0.2119</v>
@@ -2661,7 +2661,7 @@
         <v>0.4797</v>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>0.1906</v>
       </c>
       <c r="D49" t="n">
         <v>-0.2276</v>
@@ -2707,7 +2707,7 @@
         <v>0.4252</v>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>0.169</v>
       </c>
       <c r="D50" t="n">
         <v>-0.2496</v>
@@ -2753,7 +2753,7 @@
         <v>0.3581</v>
       </c>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>0.1423</v>
       </c>
       <c r="D51" t="n">
         <v>-0.2767</v>
@@ -2799,7 +2799,7 @@
         <v>0.2703</v>
       </c>
       <c r="C52" t="n">
-        <v>0</v>
+        <v>0.1074</v>
       </c>
       <c r="D52" t="n">
         <v>-0.3122</v>
@@ -2845,7 +2845,7 @@
         <v>0.1157</v>
       </c>
       <c r="C53" t="n">
-        <v>0</v>
+        <v>0.046</v>
       </c>
       <c r="D53" t="n">
         <v>-0.3746</v>
@@ -2891,7 +2891,7 @@
         <v>0.005</v>
       </c>
       <c r="C54" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="D54" t="n">
         <v>-0.4193</v>
@@ -2937,7 +2937,7 @@
         <v>-0.0076</v>
       </c>
       <c r="C55" t="n">
-        <v>-0</v>
+        <v>-0.003</v>
       </c>
       <c r="D55" t="n">
         <v>-0.4244</v>
@@ -2983,7 +2983,7 @@
         <v>-0.0542</v>
       </c>
       <c r="C56" t="n">
-        <v>-0</v>
+        <v>-0.0215</v>
       </c>
       <c r="D56" t="n">
         <v>-0.4433</v>
@@ -3029,7 +3029,7 @@
         <v>-0.1226</v>
       </c>
       <c r="C57" t="n">
-        <v>-0</v>
+        <v>-0.0487</v>
       </c>
       <c r="D57" t="n">
         <v>-0.4709</v>
@@ -3075,7 +3075,7 @@
         <v>-0.2221</v>
       </c>
       <c r="C58" t="n">
-        <v>-0</v>
+        <v>-0.0883</v>
       </c>
       <c r="D58" t="n">
         <v>-0.5111</v>
@@ -3121,7 +3121,7 @@
         <v>-0.2568</v>
       </c>
       <c r="C59" t="n">
-        <v>-0</v>
+        <v>-0.1021</v>
       </c>
       <c r="D59" t="n">
         <v>-0.5251</v>
@@ -3167,7 +3167,7 @@
         <v>-0.2657</v>
       </c>
       <c r="C60" t="n">
-        <v>-0</v>
+        <v>-0.1056</v>
       </c>
       <c r="D60" t="n">
         <v>-0.5286999999999999</v>
@@ -3213,7 +3213,7 @@
         <v>-0.429</v>
       </c>
       <c r="C61" t="n">
-        <v>-0</v>
+        <v>-0.1705</v>
       </c>
       <c r="D61" t="n">
         <v>-0.5947</v>
@@ -3259,7 +3259,7 @@
         <v>-0.5031</v>
       </c>
       <c r="C62" t="n">
-        <v>-0</v>
+        <v>-0.1999</v>
       </c>
       <c r="D62" t="n">
         <v>-0.6246</v>
@@ -3305,7 +3305,7 @@
         <v>-0.5687</v>
       </c>
       <c r="C63" t="n">
-        <v>-0</v>
+        <v>-0.226</v>
       </c>
       <c r="D63" t="n">
         <v>-0.6511</v>
@@ -3351,7 +3351,7 @@
         <v>-0.8837</v>
       </c>
       <c r="C64" t="n">
-        <v>-0</v>
+        <v>-0.3512</v>
       </c>
       <c r="D64" t="n">
         <v>-0.7784</v>
@@ -3397,7 +3397,7 @@
         <v>-1.0494</v>
       </c>
       <c r="C65" t="n">
-        <v>-0</v>
+        <v>-0.417</v>
       </c>
       <c r="D65" t="n">
         <v>-0.8453000000000001</v>
@@ -3443,7 +3443,7 @@
         <v>-1.0799</v>
       </c>
       <c r="C66" t="n">
-        <v>-0</v>
+        <v>-0.4292</v>
       </c>
       <c r="D66" t="n">
         <v>-0.8576</v>
@@ -3489,7 +3489,7 @@
         <v>-1.3488</v>
       </c>
       <c r="C67" t="n">
-        <v>-0</v>
+        <v>-0.536</v>
       </c>
       <c r="D67" t="n">
         <v>-0.9661999999999999</v>
@@ -3535,7 +3535,7 @@
         <v>-1.6529</v>
       </c>
       <c r="C68" t="n">
-        <v>-0</v>
+        <v>-0.6569</v>
       </c>
       <c r="D68" t="n">
         <v>-1.0891</v>
@@ -3581,7 +3581,7 @@
         <v>-1.7377</v>
       </c>
       <c r="C69" t="n">
-        <v>-0</v>
+        <v>-0.6906</v>
       </c>
       <c r="D69" t="n">
         <v>-1.1234</v>
@@ -3627,7 +3627,7 @@
         <v>-1.7408</v>
       </c>
       <c r="C70" t="n">
-        <v>-0</v>
+        <v>-0.6918</v>
       </c>
       <c r="D70" t="n">
         <v>-1.1246</v>
@@ -3673,7 +3673,7 @@
         <v>-1.8369</v>
       </c>
       <c r="C71" t="n">
-        <v>-0</v>
+        <v>-0.73</v>
       </c>
       <c r="D71" t="n">
         <v>-1.1634</v>
@@ -3719,7 +3719,7 @@
         <v>-1.8958</v>
       </c>
       <c r="C72" t="n">
-        <v>-0</v>
+        <v>-0.7534</v>
       </c>
       <c r="D72" t="n">
         <v>-1.1872</v>
@@ -3765,7 +3765,7 @@
         <v>-2.0034</v>
       </c>
       <c r="C73" t="n">
-        <v>-0</v>
+        <v>-0.7962</v>
       </c>
       <c r="D73" t="n">
         <v>-1.2307</v>
@@ -3811,7 +3811,7 @@
         <v>-2.0852</v>
       </c>
       <c r="C74" t="n">
-        <v>-0</v>
+        <v>-0.8287</v>
       </c>
       <c r="D74" t="n">
         <v>-1.2637</v>
@@ -3857,7 +3857,7 @@
         <v>-2.6752</v>
       </c>
       <c r="C75" t="n">
-        <v>-0</v>
+        <v>-1.0631</v>
       </c>
       <c r="D75" t="n">
         <v>-1.5021</v>
@@ -3903,7 +3903,7 @@
         <v>-2.7045</v>
       </c>
       <c r="C76" t="n">
-        <v>-0</v>
+        <v>-1.0748</v>
       </c>
       <c r="D76" t="n">
         <v>-1.5139</v>
@@ -3949,7 +3949,7 @@
         <v>-3.1415</v>
       </c>
       <c r="C77" t="n">
-        <v>-0</v>
+        <v>-1.2484</v>
       </c>
       <c r="D77" t="n">
         <v>-1.6905</v>
@@ -3995,7 +3995,7 @@
         <v>-3.5625</v>
       </c>
       <c r="C78" t="n">
-        <v>-0</v>
+        <v>-1.4158</v>
       </c>
       <c r="D78" t="n">
         <v>-1.8605</v>
@@ -4041,7 +4041,7 @@
         <v>-3.6665</v>
       </c>
       <c r="C79" t="n">
-        <v>-0</v>
+        <v>-1.4571</v>
       </c>
       <c r="D79" t="n">
         <v>-1.9025</v>
@@ -4087,7 +4087,7 @@
         <v>-3.6992</v>
       </c>
       <c r="C80" t="n">
-        <v>-0</v>
+        <v>-1.4701</v>
       </c>
       <c r="D80" t="n">
         <v>-1.9158</v>
@@ -4133,7 +4133,7 @@
         <v>-4.0028</v>
       </c>
       <c r="C81" t="n">
-        <v>-0</v>
+        <v>-1.5907</v>
       </c>
       <c r="D81" t="n">
         <v>-2.0384</v>
@@ -4179,7 +4179,7 @@
         <v>-5.2842</v>
       </c>
       <c r="C82" t="n">
-        <v>-0</v>
+        <v>-2.1</v>
       </c>
       <c r="D82" t="n">
         <v>-2.5561</v>

--- a/database/event/8045/event_8045_evp_summary.xlsx
+++ b/database/event/8045/event_8045_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>4.5742</v>
       </c>
       <c r="D2" t="n">
-        <v>4.2285</v>
+        <v>4.1418</v>
       </c>
       <c r="E2" t="n">
         <v>11.5103</v>
@@ -548,7 +548,7 @@
         <v>3.1085</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7385</v>
+        <v>2.6723</v>
       </c>
       <c r="E3" t="n">
         <v>7.8219</v>
@@ -594,7 +594,7 @@
         <v>2.7737</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3982</v>
+        <v>2.3367</v>
       </c>
       <c r="E4" t="n">
         <v>6.9795</v>
@@ -634,25 +634,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.7354</v>
+        <v>6.7211</v>
       </c>
       <c r="C5" t="n">
-        <v>2.6767</v>
+        <v>2.671</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2996</v>
+        <v>2.2338</v>
       </c>
       <c r="E5" t="n">
-        <v>6.7354</v>
+        <v>6.7211</v>
       </c>
       <c r="F5" t="n">
-        <v>3.8349</v>
+        <v>3.8206</v>
       </c>
       <c r="G5" t="n">
         <v>2.9005</v>
       </c>
       <c r="H5" t="n">
-        <v>3.8349</v>
+        <v>3.8206</v>
       </c>
       <c r="I5" t="n">
         <v>3.8527</v>
@@ -680,25 +680,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.0511</v>
+        <v>6.0389</v>
       </c>
       <c r="C6" t="n">
-        <v>2.4047</v>
+        <v>2.3999</v>
       </c>
       <c r="D6" t="n">
-        <v>2.0231</v>
+        <v>1.962</v>
       </c>
       <c r="E6" t="n">
-        <v>6.0511</v>
+        <v>6.0389</v>
       </c>
       <c r="F6" t="n">
-        <v>4.7438</v>
+        <v>4.7316</v>
       </c>
       <c r="G6" t="n">
         <v>1.3073</v>
       </c>
       <c r="H6" t="n">
-        <v>5.1352</v>
+        <v>5.1161</v>
       </c>
       <c r="I6" t="n">
         <v>5.1591</v>
@@ -726,25 +726,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.9345</v>
+        <v>5.9244</v>
       </c>
       <c r="C7" t="n">
-        <v>2.3584</v>
+        <v>2.3544</v>
       </c>
       <c r="D7" t="n">
-        <v>1.976</v>
+        <v>1.9164</v>
       </c>
       <c r="E7" t="n">
-        <v>5.9345</v>
+        <v>5.9244</v>
       </c>
       <c r="F7" t="n">
-        <v>4.1799</v>
+        <v>4.1698</v>
       </c>
       <c r="G7" t="n">
         <v>1.7546</v>
       </c>
       <c r="H7" t="n">
-        <v>4.2511</v>
+        <v>4.2352</v>
       </c>
       <c r="I7" t="n">
         <v>4.2709</v>
@@ -778,7 +778,7 @@
         <v>2.283</v>
       </c>
       <c r="D8" t="n">
-        <v>1.8994</v>
+        <v>1.8448</v>
       </c>
       <c r="E8" t="n">
         <v>5.7447</v>
@@ -814,93 +814,93 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>sjuush</t>
+          <t>Staehr</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.5098</v>
+        <v>5.4963</v>
       </c>
       <c r="C9" t="n">
-        <v>2.1896</v>
+        <v>2.1843</v>
       </c>
       <c r="D9" t="n">
-        <v>1.8045</v>
+        <v>1.7458</v>
       </c>
       <c r="E9" t="n">
-        <v>5.5098</v>
+        <v>5.4963</v>
       </c>
       <c r="F9" t="n">
-        <v>5.7523</v>
+        <v>-0.434</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.2425</v>
+        <v>5.9303</v>
       </c>
       <c r="H9" t="n">
-        <v>6.7166</v>
+        <v>-0.434</v>
       </c>
       <c r="I9" t="n">
-        <v>6.7478</v>
+        <v>-0.434</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.2425</v>
+        <v>5.9303</v>
       </c>
       <c r="K9" t="n">
-        <v>266</v>
+        <v>214</v>
       </c>
       <c r="L9" t="n">
-        <v>45</v>
+        <v>218</v>
       </c>
       <c r="M9" t="n">
-        <v>6.5053</v>
+        <v>5.4963</v>
       </c>
       <c r="N9" t="n">
-        <v>311</v>
+        <v>432</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Staehr</t>
+          <t>sjuush</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5.4963</v>
+        <v>5.4938</v>
       </c>
       <c r="C10" t="n">
-        <v>2.1843</v>
+        <v>2.1833</v>
       </c>
       <c r="D10" t="n">
-        <v>1.799</v>
+        <v>1.7448</v>
       </c>
       <c r="E10" t="n">
-        <v>5.4963</v>
+        <v>5.4938</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.434</v>
+        <v>5.7363</v>
       </c>
       <c r="G10" t="n">
-        <v>5.9303</v>
+        <v>-0.2425</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.434</v>
+        <v>6.6915</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.434</v>
+        <v>6.7478</v>
       </c>
       <c r="J10" t="n">
-        <v>5.9303</v>
+        <v>-0.2425</v>
       </c>
       <c r="K10" t="n">
-        <v>214</v>
+        <v>266</v>
       </c>
       <c r="L10" t="n">
-        <v>218</v>
+        <v>45</v>
       </c>
       <c r="M10" t="n">
-        <v>5.4963</v>
+        <v>6.5053</v>
       </c>
       <c r="N10" t="n">
-        <v>432</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11">
@@ -910,25 +910,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5.4263</v>
+        <v>5.4116</v>
       </c>
       <c r="C11" t="n">
-        <v>2.1564</v>
+        <v>2.1506</v>
       </c>
       <c r="D11" t="n">
-        <v>1.7707</v>
+        <v>1.7121</v>
       </c>
       <c r="E11" t="n">
-        <v>5.4263</v>
+        <v>5.4116</v>
       </c>
       <c r="F11" t="n">
-        <v>5.4263</v>
+        <v>5.4116</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>6.2054</v>
+        <v>6.1822</v>
       </c>
       <c r="I11" t="n">
         <v>6.2343</v>
@@ -956,25 +956,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5.0263</v>
+        <v>5.0112</v>
       </c>
       <c r="C12" t="n">
-        <v>1.9975</v>
+        <v>1.9915</v>
       </c>
       <c r="D12" t="n">
-        <v>1.6092</v>
+        <v>1.5526</v>
       </c>
       <c r="E12" t="n">
-        <v>5.0263</v>
+        <v>5.0112</v>
       </c>
       <c r="F12" t="n">
-        <v>4.0317</v>
+        <v>4.0166</v>
       </c>
       <c r="G12" t="n">
         <v>0.9946</v>
       </c>
       <c r="H12" t="n">
-        <v>4.0317</v>
+        <v>4.0166</v>
       </c>
       <c r="I12" t="n">
         <v>4.0505</v>
@@ -1002,25 +1002,25 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4.8084</v>
+        <v>4.7951</v>
       </c>
       <c r="C13" t="n">
-        <v>1.9109</v>
+        <v>1.9056</v>
       </c>
       <c r="D13" t="n">
-        <v>1.5211</v>
+        <v>1.4665</v>
       </c>
       <c r="E13" t="n">
-        <v>4.8084</v>
+        <v>4.7951</v>
       </c>
       <c r="F13" t="n">
-        <v>3.585</v>
+        <v>3.5717</v>
       </c>
       <c r="G13" t="n">
         <v>1.2234</v>
       </c>
       <c r="H13" t="n">
-        <v>3.585</v>
+        <v>3.5717</v>
       </c>
       <c r="I13" t="n">
         <v>3.6017</v>
@@ -1054,7 +1054,7 @@
         <v>1.7508</v>
       </c>
       <c r="D14" t="n">
-        <v>1.3584</v>
+        <v>1.3112</v>
       </c>
       <c r="E14" t="n">
         <v>4.4055</v>
@@ -1100,7 +1100,7 @@
         <v>1.6721</v>
       </c>
       <c r="D15" t="n">
-        <v>1.2784</v>
+        <v>1.2324</v>
       </c>
       <c r="E15" t="n">
         <v>4.2076</v>
@@ -1146,7 +1146,7 @@
         <v>1.5647</v>
       </c>
       <c r="D16" t="n">
-        <v>1.1692</v>
+        <v>1.1247</v>
       </c>
       <c r="E16" t="n">
         <v>3.9373</v>
@@ -1192,7 +1192,7 @@
         <v>1.4795</v>
       </c>
       <c r="D17" t="n">
-        <v>1.0826</v>
+        <v>1.0393</v>
       </c>
       <c r="E17" t="n">
         <v>3.7229</v>
@@ -1238,7 +1238,7 @@
         <v>1.4335</v>
       </c>
       <c r="D18" t="n">
-        <v>1.0359</v>
+        <v>0.9932</v>
       </c>
       <c r="E18" t="n">
         <v>3.6072</v>
@@ -1284,7 +1284,7 @@
         <v>1.4211</v>
       </c>
       <c r="D19" t="n">
-        <v>1.0233</v>
+        <v>0.9808</v>
       </c>
       <c r="E19" t="n">
         <v>3.576</v>
@@ -1324,25 +1324,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.3353</v>
+        <v>3.3319</v>
       </c>
       <c r="C20" t="n">
-        <v>1.3255</v>
+        <v>1.3241</v>
       </c>
       <c r="D20" t="n">
-        <v>0.926</v>
+        <v>0.8835</v>
       </c>
       <c r="E20" t="n">
-        <v>3.3353</v>
+        <v>3.3319</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9109</v>
+        <v>0.9075</v>
       </c>
       <c r="G20" t="n">
         <v>2.4245</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9109</v>
+        <v>0.9075</v>
       </c>
       <c r="I20" t="n">
         <v>0.9151</v>
@@ -1376,7 +1376,7 @@
         <v>1.2941</v>
       </c>
       <c r="D21" t="n">
-        <v>0.8942</v>
+        <v>0.8535</v>
       </c>
       <c r="E21" t="n">
         <v>3.2565</v>
@@ -1416,25 +1416,25 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3.1025</v>
+        <v>3.0899</v>
       </c>
       <c r="C22" t="n">
-        <v>1.2329</v>
+        <v>1.2279</v>
       </c>
       <c r="D22" t="n">
-        <v>0.832</v>
+        <v>0.7871</v>
       </c>
       <c r="E22" t="n">
-        <v>3.1025</v>
+        <v>3.0899</v>
       </c>
       <c r="F22" t="n">
-        <v>3.3611</v>
+        <v>3.3485</v>
       </c>
       <c r="G22" t="n">
         <v>-0.2586</v>
       </c>
       <c r="H22" t="n">
-        <v>3.3611</v>
+        <v>3.3485</v>
       </c>
       <c r="I22" t="n">
         <v>3.3767</v>
@@ -1468,7 +1468,7 @@
         <v>1.1921</v>
       </c>
       <c r="D23" t="n">
-        <v>0.7905</v>
+        <v>0.7512</v>
       </c>
       <c r="E23" t="n">
         <v>2.9998</v>
@@ -1508,25 +1508,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.8508</v>
+        <v>2.8486</v>
       </c>
       <c r="C24" t="n">
-        <v>1.1329</v>
+        <v>1.132</v>
       </c>
       <c r="D24" t="n">
-        <v>0.7302999999999999</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>2.8508</v>
+        <v>2.8486</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6037</v>
+        <v>0.6015</v>
       </c>
       <c r="G24" t="n">
         <v>2.2471</v>
       </c>
       <c r="H24" t="n">
-        <v>0.6037</v>
+        <v>0.6015</v>
       </c>
       <c r="I24" t="n">
         <v>0.6065</v>
@@ -1560,7 +1560,7 @@
         <v>1.093</v>
       </c>
       <c r="D25" t="n">
-        <v>0.6897</v>
+        <v>0.6518</v>
       </c>
       <c r="E25" t="n">
         <v>2.7503</v>
@@ -1606,7 +1606,7 @@
         <v>1.0911</v>
       </c>
       <c r="D26" t="n">
-        <v>0.6878</v>
+        <v>0.6499</v>
       </c>
       <c r="E26" t="n">
         <v>2.7456</v>
@@ -1652,7 +1652,7 @@
         <v>1.0362</v>
       </c>
       <c r="D27" t="n">
-        <v>0.632</v>
+        <v>0.5949</v>
       </c>
       <c r="E27" t="n">
         <v>2.6075</v>
@@ -1692,25 +1692,25 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.512</v>
+        <v>2.5029</v>
       </c>
       <c r="C28" t="n">
-        <v>0.9983</v>
+        <v>0.9947</v>
       </c>
       <c r="D28" t="n">
-        <v>0.5934</v>
+        <v>0.5532</v>
       </c>
       <c r="E28" t="n">
-        <v>2.512</v>
+        <v>2.5029</v>
       </c>
       <c r="F28" t="n">
-        <v>2.4402</v>
+        <v>2.4311</v>
       </c>
       <c r="G28" t="n">
         <v>0.0718</v>
       </c>
       <c r="H28" t="n">
-        <v>2.4402</v>
+        <v>2.4311</v>
       </c>
       <c r="I28" t="n">
         <v>2.4516</v>
@@ -1738,25 +1738,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2.045</v>
+        <v>2.0374</v>
       </c>
       <c r="C29" t="n">
-        <v>0.8127</v>
+        <v>0.8097</v>
       </c>
       <c r="D29" t="n">
-        <v>0.4048</v>
+        <v>0.3678</v>
       </c>
       <c r="E29" t="n">
-        <v>2.045</v>
+        <v>2.0374</v>
       </c>
       <c r="F29" t="n">
-        <v>2.045</v>
+        <v>2.0374</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>2.045</v>
+        <v>2.0374</v>
       </c>
       <c r="I29" t="n">
         <v>2.0545</v>
@@ -1790,7 +1790,7 @@
         <v>0.781</v>
       </c>
       <c r="D30" t="n">
-        <v>0.3726</v>
+        <v>0.3391</v>
       </c>
       <c r="E30" t="n">
         <v>1.9653</v>
@@ -1836,7 +1836,7 @@
         <v>0.7249</v>
       </c>
       <c r="D31" t="n">
-        <v>0.3155</v>
+        <v>0.2828</v>
       </c>
       <c r="E31" t="n">
         <v>1.824</v>
@@ -1882,7 +1882,7 @@
         <v>0.6947</v>
       </c>
       <c r="D32" t="n">
-        <v>0.2848</v>
+        <v>0.2525</v>
       </c>
       <c r="E32" t="n">
         <v>1.7481</v>
@@ -1918,93 +1918,93 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>b1t</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.7272</v>
+        <v>1.7216</v>
       </c>
       <c r="C33" t="n">
-        <v>0.6864</v>
+        <v>0.6842</v>
       </c>
       <c r="D33" t="n">
-        <v>0.2764</v>
+        <v>0.242</v>
       </c>
       <c r="E33" t="n">
-        <v>1.7272</v>
+        <v>1.7216</v>
       </c>
       <c r="F33" t="n">
-        <v>2.0336</v>
+        <v>2.5981</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.3064</v>
+        <v>-0.8764999999999999</v>
       </c>
       <c r="H33" t="n">
-        <v>2.0336</v>
+        <v>2.5981</v>
       </c>
       <c r="I33" t="n">
-        <v>2.0431</v>
+        <v>2.5981</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.3064</v>
+        <v>-0.8764999999999999</v>
       </c>
       <c r="K33" t="n">
-        <v>285</v>
+        <v>176</v>
       </c>
       <c r="L33" t="n">
-        <v>106</v>
+        <v>69</v>
       </c>
       <c r="M33" t="n">
-        <v>1.7367</v>
+        <v>1.7216</v>
       </c>
       <c r="N33" t="n">
-        <v>391</v>
+        <v>245</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>b1t</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.7216</v>
+        <v>1.7196</v>
       </c>
       <c r="C34" t="n">
-        <v>0.6842</v>
+        <v>0.6834</v>
       </c>
       <c r="D34" t="n">
-        <v>0.2741</v>
+        <v>0.2412</v>
       </c>
       <c r="E34" t="n">
-        <v>1.7216</v>
+        <v>1.7196</v>
       </c>
       <c r="F34" t="n">
-        <v>2.5981</v>
+        <v>2.026</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.8764999999999999</v>
+        <v>-0.3064</v>
       </c>
       <c r="H34" t="n">
-        <v>2.5981</v>
+        <v>2.026</v>
       </c>
       <c r="I34" t="n">
-        <v>2.5981</v>
+        <v>2.0431</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.8764999999999999</v>
+        <v>-0.3064</v>
       </c>
       <c r="K34" t="n">
-        <v>176</v>
+        <v>285</v>
       </c>
       <c r="L34" t="n">
-        <v>69</v>
+        <v>106</v>
       </c>
       <c r="M34" t="n">
-        <v>1.7216</v>
+        <v>1.7367</v>
       </c>
       <c r="N34" t="n">
-        <v>245</v>
+        <v>391</v>
       </c>
     </row>
     <row r="35">
@@ -2020,7 +2020,7 @@
         <v>0.6588000000000001</v>
       </c>
       <c r="D35" t="n">
-        <v>0.2483</v>
+        <v>0.2165</v>
       </c>
       <c r="E35" t="n">
         <v>1.6577</v>
@@ -2060,25 +2060,25 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1.6041</v>
+        <v>1.6033</v>
       </c>
       <c r="C36" t="n">
-        <v>0.6375</v>
+        <v>0.6372</v>
       </c>
       <c r="D36" t="n">
-        <v>0.2267</v>
+        <v>0.1948</v>
       </c>
       <c r="E36" t="n">
-        <v>1.6041</v>
+        <v>1.6033</v>
       </c>
       <c r="F36" t="n">
-        <v>0.2241</v>
+        <v>0.2233</v>
       </c>
       <c r="G36" t="n">
         <v>1.38</v>
       </c>
       <c r="H36" t="n">
-        <v>0.2241</v>
+        <v>0.2233</v>
       </c>
       <c r="I36" t="n">
         <v>0.2252</v>
@@ -2112,7 +2112,7 @@
         <v>0.5908</v>
       </c>
       <c r="D37" t="n">
-        <v>0.1792</v>
+        <v>0.1484</v>
       </c>
       <c r="E37" t="n">
         <v>1.4867</v>
@@ -2158,7 +2158,7 @@
         <v>0.4564</v>
       </c>
       <c r="D38" t="n">
-        <v>0.0426</v>
+        <v>0.0136</v>
       </c>
       <c r="E38" t="n">
         <v>1.1484</v>
@@ -2204,7 +2204,7 @@
         <v>0.4127</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.0018</v>
+        <v>-0.0302</v>
       </c>
       <c r="E39" t="n">
         <v>1.0385</v>
@@ -2244,25 +2244,25 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.9902</v>
+        <v>0.9868</v>
       </c>
       <c r="C40" t="n">
-        <v>0.3935</v>
+        <v>0.3922</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.0213</v>
+        <v>-0.0508</v>
       </c>
       <c r="E40" t="n">
-        <v>0.9902</v>
+        <v>0.9868</v>
       </c>
       <c r="F40" t="n">
-        <v>0.9028</v>
+        <v>0.8994</v>
       </c>
       <c r="G40" t="n">
         <v>0.08740000000000001</v>
       </c>
       <c r="H40" t="n">
-        <v>0.9028</v>
+        <v>0.8994</v>
       </c>
       <c r="I40" t="n">
         <v>0.907</v>
@@ -2296,7 +2296,7 @@
         <v>0.3652</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.0501</v>
+        <v>-0.07779999999999999</v>
       </c>
       <c r="E41" t="n">
         <v>0.9189000000000001</v>
@@ -2342,7 +2342,7 @@
         <v>0.3399</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.07580000000000001</v>
+        <v>-0.1031</v>
       </c>
       <c r="E42" t="n">
         <v>0.8554</v>
@@ -2388,7 +2388,7 @@
         <v>0.3212</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.0949</v>
+        <v>-0.1219</v>
       </c>
       <c r="E43" t="n">
         <v>0.8082</v>
@@ -2428,25 +2428,25 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.7408</v>
+        <v>0.738</v>
       </c>
       <c r="C44" t="n">
-        <v>0.2944</v>
+        <v>0.2933</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.1221</v>
+        <v>-0.1499</v>
       </c>
       <c r="E44" t="n">
-        <v>0.7408</v>
+        <v>0.738</v>
       </c>
       <c r="F44" t="n">
-        <v>0.7408</v>
+        <v>0.738</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.7408</v>
+        <v>0.738</v>
       </c>
       <c r="I44" t="n">
         <v>0.7442</v>
@@ -2480,7 +2480,7 @@
         <v>0.2908</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.1258</v>
+        <v>-0.1524</v>
       </c>
       <c r="E45" t="n">
         <v>0.7317</v>
@@ -2526,7 +2526,7 @@
         <v>0.2262</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.1914</v>
+        <v>-0.2171</v>
       </c>
       <c r="E46" t="n">
         <v>0.5693</v>
@@ -2572,7 +2572,7 @@
         <v>0.2189</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.1989</v>
+        <v>-0.2245</v>
       </c>
       <c r="E47" t="n">
         <v>0.5508</v>
@@ -2618,7 +2618,7 @@
         <v>0.206</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.2119</v>
+        <v>-0.2374</v>
       </c>
       <c r="E48" t="n">
         <v>0.5184</v>
@@ -2664,7 +2664,7 @@
         <v>0.1906</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.2276</v>
+        <v>-0.2528</v>
       </c>
       <c r="E49" t="n">
         <v>0.4797</v>
@@ -2710,7 +2710,7 @@
         <v>0.169</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.2496</v>
+        <v>-0.2745</v>
       </c>
       <c r="E50" t="n">
         <v>0.4252</v>
@@ -2750,25 +2750,25 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.3581</v>
+        <v>0.3568</v>
       </c>
       <c r="C51" t="n">
-        <v>0.1423</v>
+        <v>0.1418</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.2767</v>
+        <v>-0.3018</v>
       </c>
       <c r="E51" t="n">
-        <v>0.3581</v>
+        <v>0.3568</v>
       </c>
       <c r="F51" t="n">
-        <v>0.3581</v>
+        <v>0.3568</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>0.3581</v>
+        <v>0.3568</v>
       </c>
       <c r="I51" t="n">
         <v>0.3598</v>
@@ -2802,7 +2802,7 @@
         <v>0.1074</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.3122</v>
+        <v>-0.3362</v>
       </c>
       <c r="E52" t="n">
         <v>0.2703</v>
@@ -2848,7 +2848,7 @@
         <v>0.046</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.3746</v>
+        <v>-0.3978</v>
       </c>
       <c r="E53" t="n">
         <v>0.1157</v>
@@ -2894,7 +2894,7 @@
         <v>0.002</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.4193</v>
+        <v>-0.4419</v>
       </c>
       <c r="E54" t="n">
         <v>0.005</v>
@@ -2940,7 +2940,7 @@
         <v>-0.003</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.4244</v>
+        <v>-0.4469</v>
       </c>
       <c r="E55" t="n">
         <v>-0.0076</v>
@@ -2980,25 +2980,25 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.0542</v>
+        <v>-0.0577</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.0215</v>
+        <v>-0.0229</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.4433</v>
+        <v>-0.4669</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.0542</v>
+        <v>-0.0577</v>
       </c>
       <c r="F56" t="n">
-        <v>0.9458</v>
+        <v>0.9423</v>
       </c>
       <c r="G56" t="n">
         <v>-1</v>
       </c>
       <c r="H56" t="n">
-        <v>0.9458</v>
+        <v>0.9423</v>
       </c>
       <c r="I56" t="n">
         <v>0.9502</v>
@@ -3032,7 +3032,7 @@
         <v>-0.0487</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.4709</v>
+        <v>-0.4928</v>
       </c>
       <c r="E57" t="n">
         <v>-0.1226</v>
@@ -3078,7 +3078,7 @@
         <v>-0.0883</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.5111</v>
+        <v>-0.5324</v>
       </c>
       <c r="E58" t="n">
         <v>-0.2221</v>
@@ -3124,7 +3124,7 @@
         <v>-0.1021</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.5251</v>
+        <v>-0.5462</v>
       </c>
       <c r="E59" t="n">
         <v>-0.2568</v>
@@ -3170,7 +3170,7 @@
         <v>-0.1056</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.5286999999999999</v>
+        <v>-0.5498</v>
       </c>
       <c r="E60" t="n">
         <v>-0.2657</v>
@@ -3216,7 +3216,7 @@
         <v>-0.1705</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.5947</v>
+        <v>-0.6148</v>
       </c>
       <c r="E61" t="n">
         <v>-0.429</v>
@@ -3262,7 +3262,7 @@
         <v>-0.1999</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.6246</v>
+        <v>-0.6443</v>
       </c>
       <c r="E62" t="n">
         <v>-0.5031</v>
@@ -3302,25 +3302,25 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.5687</v>
+        <v>-0.573</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.226</v>
+        <v>-0.2277</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.6511</v>
+        <v>-0.6722</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.5687</v>
+        <v>-0.573</v>
       </c>
       <c r="F63" t="n">
-        <v>1.1361</v>
+        <v>1.1318</v>
       </c>
       <c r="G63" t="n">
         <v>-1.7048</v>
       </c>
       <c r="H63" t="n">
-        <v>1.1361</v>
+        <v>1.1318</v>
       </c>
       <c r="I63" t="n">
         <v>1.1413</v>
@@ -3354,7 +3354,7 @@
         <v>-0.3512</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.7784</v>
+        <v>-0.796</v>
       </c>
       <c r="E64" t="n">
         <v>-0.8837</v>
@@ -3400,7 +3400,7 @@
         <v>-0.417</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.8453000000000001</v>
+        <v>-0.862</v>
       </c>
       <c r="E65" t="n">
         <v>-1.0494</v>
@@ -3446,7 +3446,7 @@
         <v>-0.4292</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.8576</v>
+        <v>-0.8741</v>
       </c>
       <c r="E66" t="n">
         <v>-1.0799</v>
@@ -3492,7 +3492,7 @@
         <v>-0.536</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.9661999999999999</v>
+        <v>-0.9813</v>
       </c>
       <c r="E67" t="n">
         <v>-1.3488</v>
@@ -3538,7 +3538,7 @@
         <v>-0.6569</v>
       </c>
       <c r="D68" t="n">
-        <v>-1.0891</v>
+        <v>-1.1024</v>
       </c>
       <c r="E68" t="n">
         <v>-1.6529</v>
@@ -3578,25 +3578,25 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-1.7377</v>
+        <v>-1.735</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.6906</v>
+        <v>-0.6895</v>
       </c>
       <c r="D69" t="n">
-        <v>-1.1234</v>
+        <v>-1.1351</v>
       </c>
       <c r="E69" t="n">
-        <v>-1.7377</v>
+        <v>-1.735</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.7377</v>
+        <v>-0.735</v>
       </c>
       <c r="G69" t="n">
         <v>-1</v>
       </c>
       <c r="H69" t="n">
-        <v>-0.7377</v>
+        <v>-0.735</v>
       </c>
       <c r="I69" t="n">
         <v>-0.7412</v>
@@ -3630,7 +3630,7 @@
         <v>-0.6918</v>
       </c>
       <c r="D70" t="n">
-        <v>-1.1246</v>
+        <v>-1.1374</v>
       </c>
       <c r="E70" t="n">
         <v>-1.7408</v>
@@ -3670,25 +3670,25 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-1.8369</v>
+        <v>-1.8338</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.73</v>
+        <v>-0.7288</v>
       </c>
       <c r="D71" t="n">
-        <v>-1.1634</v>
+        <v>-1.1745</v>
       </c>
       <c r="E71" t="n">
-        <v>-1.8369</v>
+        <v>-1.8338</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.8369</v>
+        <v>-0.8338</v>
       </c>
       <c r="G71" t="n">
         <v>-1</v>
       </c>
       <c r="H71" t="n">
-        <v>-0.8369</v>
+        <v>-0.8338</v>
       </c>
       <c r="I71" t="n">
         <v>-0.8408</v>
@@ -3722,7 +3722,7 @@
         <v>-0.7534</v>
       </c>
       <c r="D72" t="n">
-        <v>-1.1872</v>
+        <v>-1.1992</v>
       </c>
       <c r="E72" t="n">
         <v>-1.8958</v>
@@ -3768,7 +3768,7 @@
         <v>-0.7962</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.2307</v>
+        <v>-1.2421</v>
       </c>
       <c r="E73" t="n">
         <v>-2.0034</v>
@@ -3814,7 +3814,7 @@
         <v>-0.8287</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.2637</v>
+        <v>-1.2747</v>
       </c>
       <c r="E74" t="n">
         <v>-2.0852</v>
@@ -3860,7 +3860,7 @@
         <v>-1.0631</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.5021</v>
+        <v>-1.5097</v>
       </c>
       <c r="E75" t="n">
         <v>-2.6752</v>
@@ -3906,7 +3906,7 @@
         <v>-1.0748</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.5139</v>
+        <v>-1.5214</v>
       </c>
       <c r="E76" t="n">
         <v>-2.7045</v>
@@ -3952,7 +3952,7 @@
         <v>-1.2484</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.6905</v>
+        <v>-1.6955</v>
       </c>
       <c r="E77" t="n">
         <v>-3.1415</v>
@@ -3992,25 +3992,25 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-3.5625</v>
+        <v>-3.5533</v>
       </c>
       <c r="C78" t="n">
-        <v>-1.4158</v>
+        <v>-1.4121</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.8605</v>
+        <v>-1.8595</v>
       </c>
       <c r="E78" t="n">
-        <v>-3.5625</v>
+        <v>-3.5533</v>
       </c>
       <c r="F78" t="n">
-        <v>-2.4672</v>
+        <v>-2.458</v>
       </c>
       <c r="G78" t="n">
         <v>-1.0953</v>
       </c>
       <c r="H78" t="n">
-        <v>-2.4672</v>
+        <v>-2.458</v>
       </c>
       <c r="I78" t="n">
         <v>-2.4786</v>
@@ -4038,25 +4038,25 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-3.6665</v>
+        <v>-3.6542</v>
       </c>
       <c r="C79" t="n">
-        <v>-1.4571</v>
+        <v>-1.4522</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.9025</v>
+        <v>-1.8997</v>
       </c>
       <c r="E79" t="n">
-        <v>-3.6665</v>
+        <v>-3.6542</v>
       </c>
       <c r="F79" t="n">
-        <v>-3.3</v>
+        <v>-3.2877</v>
       </c>
       <c r="G79" t="n">
         <v>-0.3665</v>
       </c>
       <c r="H79" t="n">
-        <v>-3.3</v>
+        <v>-3.2877</v>
       </c>
       <c r="I79" t="n">
         <v>-3.3154</v>
@@ -4090,7 +4090,7 @@
         <v>-1.4701</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.9158</v>
+        <v>-1.9177</v>
       </c>
       <c r="E80" t="n">
         <v>-3.6992</v>
@@ -4136,7 +4136,7 @@
         <v>-1.5907</v>
       </c>
       <c r="D81" t="n">
-        <v>-2.0384</v>
+        <v>-2.0386</v>
       </c>
       <c r="E81" t="n">
         <v>-4.0028</v>
@@ -4176,25 +4176,25 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>-5.2842</v>
+        <v>-5.2675</v>
       </c>
       <c r="C82" t="n">
-        <v>-2.1</v>
+        <v>-2.0933</v>
       </c>
       <c r="D82" t="n">
-        <v>-2.5561</v>
+        <v>-2.5425</v>
       </c>
       <c r="E82" t="n">
-        <v>-5.2842</v>
+        <v>-5.2675</v>
       </c>
       <c r="F82" t="n">
-        <v>-4.4691</v>
+        <v>-4.4524</v>
       </c>
       <c r="G82" t="n">
         <v>-0.8151</v>
       </c>
       <c r="H82" t="n">
-        <v>-4.4691</v>
+        <v>-4.4524</v>
       </c>
       <c r="I82" t="n">
         <v>-4.4899</v>

--- a/database/event/8045/event_8045_evp_summary.xlsx
+++ b/database/event/8045/event_8045_evp_summary.xlsx
@@ -496,16 +496,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10.8689</v>
+        <v>11.4974</v>
       </c>
       <c r="C2" t="n">
-        <v>4.3194</v>
+        <v>4.5691</v>
       </c>
       <c r="D2" t="n">
-        <v>4.3235</v>
+        <v>4.5218</v>
       </c>
       <c r="E2" t="n">
-        <v>10.8689</v>
+        <v>11.4974</v>
       </c>
       <c r="F2" t="n">
         <v>4.6781</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.7237</v>
+        <v>7.9715</v>
       </c>
       <c r="C3" t="n">
-        <v>3.0694</v>
+        <v>3.1679</v>
       </c>
       <c r="D3" t="n">
-        <v>2.8918</v>
+        <v>2.9469</v>
       </c>
       <c r="E3" t="n">
-        <v>7.7237</v>
+        <v>7.9715</v>
       </c>
       <c r="F3" t="n">
-        <v>3.7506</v>
+        <v>3.7502</v>
       </c>
       <c r="G3" t="n">
-        <v>3.9731</v>
+        <v>3.9729</v>
       </c>
       <c r="H3" t="n">
-        <v>5.4839</v>
+        <v>5.4831</v>
       </c>
       <c r="I3" t="n">
-        <v>5.4839</v>
+        <v>5.4831</v>
       </c>
       <c r="J3" t="n">
-        <v>3.9731</v>
+        <v>3.9729</v>
       </c>
       <c r="K3" t="n">
         <v>214</v>
@@ -575,7 +575,7 @@
         <v>218</v>
       </c>
       <c r="M3" t="n">
-        <v>9.457000000000001</v>
+        <v>9.456</v>
       </c>
       <c r="N3" t="n">
         <v>432</v>
@@ -588,16 +588,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.1963</v>
+        <v>7.4228</v>
       </c>
       <c r="C4" t="n">
-        <v>2.8598</v>
+        <v>2.9499</v>
       </c>
       <c r="D4" t="n">
-        <v>2.6517</v>
+        <v>2.7018</v>
       </c>
       <c r="E4" t="n">
-        <v>7.1963</v>
+        <v>7.4228</v>
       </c>
       <c r="F4" t="n">
         <v>3.7074</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.9508</v>
+        <v>6.1614</v>
       </c>
       <c r="C5" t="n">
-        <v>2.3649</v>
+        <v>2.4486</v>
       </c>
       <c r="D5" t="n">
-        <v>2.0847</v>
+        <v>2.1383</v>
       </c>
       <c r="E5" t="n">
-        <v>5.9508</v>
+        <v>6.1614</v>
       </c>
       <c r="F5" t="n">
-        <v>4.1493</v>
+        <v>4.1491</v>
       </c>
       <c r="G5" t="n">
-        <v>1.8015</v>
+        <v>1.8016</v>
       </c>
       <c r="H5" t="n">
-        <v>6.3566</v>
+        <v>6.3562</v>
       </c>
       <c r="I5" t="n">
-        <v>6.5204</v>
+        <v>6.52</v>
       </c>
       <c r="J5" t="n">
-        <v>1.8015</v>
+        <v>1.8016</v>
       </c>
       <c r="K5" t="n">
         <v>356</v>
@@ -667,7 +667,7 @@
         <v>109</v>
       </c>
       <c r="M5" t="n">
-        <v>8.321900000000001</v>
+        <v>8.3216</v>
       </c>
       <c r="N5" t="n">
         <v>465</v>
@@ -676,139 +676,139 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>zont1x</t>
+          <t>XANTARES</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.8151</v>
+        <v>5.7727</v>
       </c>
       <c r="C6" t="n">
-        <v>2.3109</v>
+        <v>2.2941</v>
       </c>
       <c r="D6" t="n">
-        <v>2.0229</v>
+        <v>1.9647</v>
       </c>
       <c r="E6" t="n">
-        <v>5.8151</v>
+        <v>5.7727</v>
       </c>
       <c r="F6" t="n">
-        <v>1.5078</v>
+        <v>4.3373</v>
       </c>
       <c r="G6" t="n">
-        <v>4.3073</v>
+        <v>1.2365</v>
       </c>
       <c r="H6" t="n">
-        <v>1.5078</v>
+        <v>6.7681</v>
       </c>
       <c r="I6" t="n">
-        <v>1.5078</v>
+        <v>6.9426</v>
       </c>
       <c r="J6" t="n">
-        <v>4.3073</v>
+        <v>1.2365</v>
       </c>
       <c r="K6" t="n">
-        <v>132</v>
+        <v>356</v>
       </c>
       <c r="L6" t="n">
-        <v>195</v>
+        <v>109</v>
       </c>
       <c r="M6" t="n">
-        <v>5.815099999999999</v>
+        <v>8.1791</v>
       </c>
       <c r="N6" t="n">
-        <v>327</v>
+        <v>465</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>KSCERATO</t>
+          <t>zont1x</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.8052</v>
+        <v>5.7668</v>
       </c>
       <c r="C7" t="n">
-        <v>2.307</v>
+        <v>2.2918</v>
       </c>
       <c r="D7" t="n">
-        <v>2.0184</v>
+        <v>1.9621</v>
       </c>
       <c r="E7" t="n">
-        <v>5.8052</v>
+        <v>5.7668</v>
       </c>
       <c r="F7" t="n">
-        <v>3.2526</v>
+        <v>1.5078</v>
       </c>
       <c r="G7" t="n">
-        <v>2.5526</v>
+        <v>4.3073</v>
       </c>
       <c r="H7" t="n">
-        <v>4.3941</v>
+        <v>1.5078</v>
       </c>
       <c r="I7" t="n">
-        <v>4.5073</v>
+        <v>1.5078</v>
       </c>
       <c r="J7" t="n">
-        <v>2.5526</v>
+        <v>4.3073</v>
       </c>
       <c r="K7" t="n">
-        <v>285</v>
+        <v>132</v>
       </c>
       <c r="L7" t="n">
-        <v>106</v>
+        <v>195</v>
       </c>
       <c r="M7" t="n">
-        <v>7.0599</v>
+        <v>5.815099999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>391</v>
+        <v>327</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>XANTARES</t>
+          <t>KSCERATO</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.5741</v>
+        <v>5.7616</v>
       </c>
       <c r="C8" t="n">
-        <v>2.2152</v>
+        <v>2.2897</v>
       </c>
       <c r="D8" t="n">
-        <v>1.9132</v>
+        <v>1.9598</v>
       </c>
       <c r="E8" t="n">
-        <v>5.5741</v>
+        <v>5.7616</v>
       </c>
       <c r="F8" t="n">
-        <v>4.3374</v>
+        <v>3.2631</v>
       </c>
       <c r="G8" t="n">
-        <v>1.2367</v>
+        <v>2.5526</v>
       </c>
       <c r="H8" t="n">
-        <v>6.7682</v>
+        <v>4.4169</v>
       </c>
       <c r="I8" t="n">
-        <v>6.9426</v>
+        <v>4.5307</v>
       </c>
       <c r="J8" t="n">
-        <v>1.2367</v>
+        <v>2.5526</v>
       </c>
       <c r="K8" t="n">
-        <v>356</v>
+        <v>285</v>
       </c>
       <c r="L8" t="n">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="M8" t="n">
-        <v>8.1793</v>
+        <v>7.0833</v>
       </c>
       <c r="N8" t="n">
-        <v>465</v>
+        <v>391</v>
       </c>
     </row>
     <row r="9">
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.5198</v>
+        <v>5.6609</v>
       </c>
       <c r="C9" t="n">
-        <v>2.1936</v>
+        <v>2.2497</v>
       </c>
       <c r="D9" t="n">
-        <v>1.8885</v>
+        <v>1.9148</v>
       </c>
       <c r="E9" t="n">
-        <v>5.5198</v>
+        <v>5.6609</v>
       </c>
       <c r="F9" t="n">
-        <v>0.137</v>
+        <v>0.1577</v>
       </c>
       <c r="G9" t="n">
-        <v>5.3828</v>
+        <v>5.3969</v>
       </c>
       <c r="H9" t="n">
-        <v>0.137</v>
+        <v>0.1577</v>
       </c>
       <c r="I9" t="n">
-        <v>0.137</v>
+        <v>0.1577</v>
       </c>
       <c r="J9" t="n">
-        <v>5.3828</v>
+        <v>5.3969</v>
       </c>
       <c r="K9" t="n">
         <v>214</v>
@@ -851,7 +851,7 @@
         <v>218</v>
       </c>
       <c r="M9" t="n">
-        <v>5.5198</v>
+        <v>5.5546</v>
       </c>
       <c r="N9" t="n">
         <v>432</v>
@@ -860,81 +860,81 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>YEKINDAR</t>
+          <t>sjuush</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.6948</v>
+        <v>5.0006</v>
       </c>
       <c r="C10" t="n">
-        <v>1.8657</v>
+        <v>1.9873</v>
       </c>
       <c r="D10" t="n">
-        <v>1.513</v>
+        <v>1.6198</v>
       </c>
       <c r="E10" t="n">
-        <v>4.6948</v>
+        <v>5.0006</v>
       </c>
       <c r="F10" t="n">
-        <v>3.4103</v>
+        <v>4.8439</v>
       </c>
       <c r="G10" t="n">
-        <v>1.2845</v>
+        <v>-0.1887</v>
       </c>
       <c r="H10" t="n">
-        <v>4.7392</v>
+        <v>7.8769</v>
       </c>
       <c r="I10" t="n">
-        <v>4.8613</v>
+        <v>8.0799</v>
       </c>
       <c r="J10" t="n">
-        <v>1.2845</v>
+        <v>-0.1887</v>
       </c>
       <c r="K10" t="n">
-        <v>285</v>
+        <v>266</v>
       </c>
       <c r="L10" t="n">
-        <v>106</v>
+        <v>45</v>
       </c>
       <c r="M10" t="n">
-        <v>6.145799999999999</v>
+        <v>7.8912</v>
       </c>
       <c r="N10" t="n">
-        <v>391</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>sjuush</t>
+          <t>r1nkle</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.6436</v>
+        <v>4.8604</v>
       </c>
       <c r="C11" t="n">
-        <v>1.8454</v>
+        <v>1.9315</v>
       </c>
       <c r="D11" t="n">
-        <v>1.4897</v>
+        <v>1.5572</v>
       </c>
       <c r="E11" t="n">
-        <v>4.6436</v>
+        <v>4.8604</v>
       </c>
       <c r="F11" t="n">
-        <v>4.8443</v>
+        <v>3.5011</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.2007</v>
+        <v>1.0569</v>
       </c>
       <c r="H11" t="n">
-        <v>7.8776</v>
+        <v>4.9379</v>
       </c>
       <c r="I11" t="n">
-        <v>8.0806</v>
+        <v>5.0651</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.2007</v>
+        <v>1.0569</v>
       </c>
       <c r="K11" t="n">
         <v>266</v>
@@ -943,7 +943,7 @@
         <v>45</v>
       </c>
       <c r="M11" t="n">
-        <v>7.8799</v>
+        <v>6.122</v>
       </c>
       <c r="N11" t="n">
         <v>311</v>
@@ -952,93 +952,93 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>r1nkle</t>
+          <t>malbsMd</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4.5495</v>
+        <v>4.7785</v>
       </c>
       <c r="C12" t="n">
-        <v>1.808</v>
+        <v>1.899</v>
       </c>
       <c r="D12" t="n">
-        <v>1.4468</v>
+        <v>1.5206</v>
       </c>
       <c r="E12" t="n">
-        <v>4.5495</v>
+        <v>4.7785</v>
       </c>
       <c r="F12" t="n">
-        <v>3.4921</v>
+        <v>4.4842</v>
       </c>
       <c r="G12" t="n">
-        <v>1.0574</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>4.9181</v>
+        <v>7.0896</v>
       </c>
       <c r="I12" t="n">
-        <v>5.0448</v>
+        <v>7.0896</v>
       </c>
       <c r="J12" t="n">
-        <v>1.0574</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="L12" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>6.1022</v>
+        <v>7.0896</v>
       </c>
       <c r="N12" t="n">
-        <v>311</v>
+        <v>276</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>malbsMd</t>
+          <t>YEKINDAR</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4.4839</v>
+        <v>4.697</v>
       </c>
       <c r="C13" t="n">
-        <v>1.7819</v>
+        <v>1.8666</v>
       </c>
       <c r="D13" t="n">
-        <v>1.417</v>
+        <v>1.4842</v>
       </c>
       <c r="E13" t="n">
-        <v>4.4839</v>
+        <v>4.697</v>
       </c>
       <c r="F13" t="n">
-        <v>4.4839</v>
+        <v>3.4045</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1.2845</v>
       </c>
       <c r="H13" t="n">
-        <v>7.089</v>
+        <v>4.7265</v>
       </c>
       <c r="I13" t="n">
-        <v>7.089</v>
+        <v>4.8483</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1.2845</v>
       </c>
       <c r="K13" t="n">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="M13" t="n">
-        <v>7.089</v>
+        <v>6.1328</v>
       </c>
       <c r="N13" t="n">
-        <v>276</v>
+        <v>391</v>
       </c>
     </row>
     <row r="14">
@@ -1048,28 +1048,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4.2641</v>
+        <v>4.6121</v>
       </c>
       <c r="C14" t="n">
-        <v>1.6946</v>
+        <v>1.8329</v>
       </c>
       <c r="D14" t="n">
-        <v>1.3169</v>
+        <v>1.4463</v>
       </c>
       <c r="E14" t="n">
-        <v>4.2641</v>
+        <v>4.6121</v>
       </c>
       <c r="F14" t="n">
-        <v>4.2641</v>
+        <v>4.2856</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>6.6079</v>
+        <v>6.6548</v>
       </c>
       <c r="I14" t="n">
-        <v>6.7782</v>
+        <v>6.8263</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1081,7 +1081,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>6.7782</v>
+        <v>6.8263</v>
       </c>
       <c r="N14" t="n">
         <v>315</v>
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.9178</v>
+        <v>3.9844</v>
       </c>
       <c r="C15" t="n">
-        <v>1.557</v>
+        <v>1.5834</v>
       </c>
       <c r="D15" t="n">
-        <v>1.1593</v>
+        <v>1.1659</v>
       </c>
       <c r="E15" t="n">
-        <v>3.9178</v>
+        <v>3.9844</v>
       </c>
       <c r="F15" t="n">
-        <v>3.5452</v>
+        <v>3.5451</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3726</v>
+        <v>0.372</v>
       </c>
       <c r="H15" t="n">
-        <v>5.0345</v>
+        <v>5.0342</v>
       </c>
       <c r="I15" t="n">
-        <v>5.0345</v>
+        <v>5.0342</v>
       </c>
       <c r="J15" t="n">
-        <v>0.3726</v>
+        <v>0.372</v>
       </c>
       <c r="K15" t="n">
         <v>214</v>
@@ -1127,7 +1127,7 @@
         <v>218</v>
       </c>
       <c r="M15" t="n">
-        <v>5.407100000000001</v>
+        <v>5.4062</v>
       </c>
       <c r="N15" t="n">
         <v>432</v>
@@ -1136,93 +1136,93 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>woxic</t>
+          <t>w0nderful</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.8884</v>
+        <v>3.9641</v>
       </c>
       <c r="C16" t="n">
-        <v>1.5453</v>
+        <v>1.5754</v>
       </c>
       <c r="D16" t="n">
-        <v>1.1459</v>
+        <v>1.1569</v>
       </c>
       <c r="E16" t="n">
-        <v>3.8884</v>
+        <v>3.9641</v>
       </c>
       <c r="F16" t="n">
-        <v>1.857</v>
+        <v>2.4805</v>
       </c>
       <c r="G16" t="n">
-        <v>2.0314</v>
+        <v>1.2614</v>
       </c>
       <c r="H16" t="n">
-        <v>1.857</v>
+        <v>2.7041</v>
       </c>
       <c r="I16" t="n">
-        <v>1.9048</v>
+        <v>2.7041</v>
       </c>
       <c r="J16" t="n">
-        <v>2.0314</v>
+        <v>1.2614</v>
       </c>
       <c r="K16" t="n">
-        <v>356</v>
+        <v>176</v>
       </c>
       <c r="L16" t="n">
-        <v>109</v>
+        <v>69</v>
       </c>
       <c r="M16" t="n">
-        <v>3.9362</v>
+        <v>3.9655</v>
       </c>
       <c r="N16" t="n">
-        <v>465</v>
+        <v>245</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>w0nderful</t>
+          <t>woxic</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3.7418</v>
+        <v>3.9069</v>
       </c>
       <c r="C17" t="n">
-        <v>1.487</v>
+        <v>1.5526</v>
       </c>
       <c r="D17" t="n">
-        <v>1.0791</v>
+        <v>1.1313</v>
       </c>
       <c r="E17" t="n">
-        <v>3.7418</v>
+        <v>3.9069</v>
       </c>
       <c r="F17" t="n">
-        <v>2.4804</v>
+        <v>1.8679</v>
       </c>
       <c r="G17" t="n">
-        <v>1.2614</v>
+        <v>2.0314</v>
       </c>
       <c r="H17" t="n">
-        <v>2.7038</v>
+        <v>1.8679</v>
       </c>
       <c r="I17" t="n">
-        <v>2.7038</v>
+        <v>1.916</v>
       </c>
       <c r="J17" t="n">
-        <v>1.2614</v>
+        <v>2.0314</v>
       </c>
       <c r="K17" t="n">
-        <v>176</v>
+        <v>356</v>
       </c>
       <c r="L17" t="n">
-        <v>69</v>
+        <v>109</v>
       </c>
       <c r="M17" t="n">
-        <v>3.9652</v>
+        <v>3.9474</v>
       </c>
       <c r="N17" t="n">
-        <v>245</v>
+        <v>465</v>
       </c>
     </row>
     <row r="18">
@@ -1232,28 +1232,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3.5531</v>
+        <v>3.8313</v>
       </c>
       <c r="C18" t="n">
-        <v>1.412</v>
+        <v>1.5226</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9932</v>
+        <v>1.0975</v>
       </c>
       <c r="E18" t="n">
-        <v>3.5531</v>
+        <v>3.8313</v>
       </c>
       <c r="F18" t="n">
-        <v>3.3665</v>
+        <v>3.3783</v>
       </c>
       <c r="G18" t="n">
         <v>0.1866</v>
       </c>
       <c r="H18" t="n">
-        <v>4.6433</v>
+        <v>4.6691</v>
       </c>
       <c r="I18" t="n">
-        <v>4.6433</v>
+        <v>4.6691</v>
       </c>
       <c r="J18" t="n">
         <v>0.1866</v>
@@ -1265,7 +1265,7 @@
         <v>48</v>
       </c>
       <c r="M18" t="n">
-        <v>4.8299</v>
+        <v>4.855700000000001</v>
       </c>
       <c r="N18" t="n">
         <v>192</v>
@@ -1274,173 +1274,173 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>yuurih</t>
+          <t>ksloks</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.5231</v>
+        <v>3.7576</v>
       </c>
       <c r="C19" t="n">
-        <v>1.4001</v>
+        <v>1.4933</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9796</v>
+        <v>1.0646</v>
       </c>
       <c r="E19" t="n">
-        <v>3.5231</v>
+        <v>3.7576</v>
       </c>
       <c r="F19" t="n">
-        <v>1.9036</v>
+        <v>3.5031</v>
       </c>
       <c r="G19" t="n">
-        <v>1.6195</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.9036</v>
+        <v>4.9422</v>
       </c>
       <c r="I19" t="n">
-        <v>1.9527</v>
+        <v>4.9422</v>
       </c>
       <c r="J19" t="n">
-        <v>1.6195</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>285</v>
+        <v>240</v>
       </c>
       <c r="L19" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.5722</v>
+        <v>4.9422</v>
       </c>
       <c r="N19" t="n">
-        <v>391</v>
+        <v>240</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Aleksib</t>
+          <t>HeavyGod</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.5192</v>
+        <v>3.5862</v>
       </c>
       <c r="C20" t="n">
-        <v>1.3985</v>
+        <v>1.4252</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9778</v>
+        <v>0.9881</v>
       </c>
       <c r="E20" t="n">
-        <v>3.5192</v>
+        <v>3.5862</v>
       </c>
       <c r="F20" t="n">
-        <v>3.8235</v>
+        <v>3.4111</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.3043</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>5.6436</v>
+        <v>4.741</v>
       </c>
       <c r="I20" t="n">
-        <v>5.6436</v>
+        <v>4.741</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.3043</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>176</v>
+        <v>276</v>
       </c>
       <c r="L20" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>5.3393</v>
+        <v>4.741</v>
       </c>
       <c r="N20" t="n">
-        <v>245</v>
+        <v>276</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ksloks</t>
+          <t>Aleksib</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3.495</v>
+        <v>3.5569</v>
       </c>
       <c r="C21" t="n">
-        <v>1.3889</v>
+        <v>1.4135</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9668</v>
+        <v>0.975</v>
       </c>
       <c r="E21" t="n">
-        <v>3.495</v>
+        <v>3.5569</v>
       </c>
       <c r="F21" t="n">
-        <v>3.495</v>
+        <v>3.8237</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>-0.3043</v>
       </c>
       <c r="H21" t="n">
-        <v>4.9245</v>
+        <v>5.644</v>
       </c>
       <c r="I21" t="n">
-        <v>4.9245</v>
+        <v>5.644</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>-0.3043</v>
       </c>
       <c r="K21" t="n">
-        <v>240</v>
+        <v>176</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="M21" t="n">
-        <v>4.9245</v>
+        <v>5.339700000000001</v>
       </c>
       <c r="N21" t="n">
-        <v>240</v>
+        <v>245</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>molodoy</t>
+          <t>yuurih</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3.426</v>
+        <v>3.5401</v>
       </c>
       <c r="C22" t="n">
-        <v>1.3615</v>
+        <v>1.4069</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9354</v>
+        <v>0.9675</v>
       </c>
       <c r="E22" t="n">
-        <v>3.426</v>
+        <v>3.5401</v>
       </c>
       <c r="F22" t="n">
-        <v>1.1592</v>
+        <v>1.9039</v>
       </c>
       <c r="G22" t="n">
-        <v>2.2668</v>
+        <v>1.6195</v>
       </c>
       <c r="H22" t="n">
-        <v>1.1592</v>
+        <v>1.9039</v>
       </c>
       <c r="I22" t="n">
-        <v>1.189</v>
+        <v>1.953</v>
       </c>
       <c r="J22" t="n">
-        <v>2.2668</v>
+        <v>1.6195</v>
       </c>
       <c r="K22" t="n">
         <v>285</v>
@@ -1449,7 +1449,7 @@
         <v>106</v>
       </c>
       <c r="M22" t="n">
-        <v>3.4558</v>
+        <v>3.5725</v>
       </c>
       <c r="N22" t="n">
         <v>391</v>
@@ -1458,47 +1458,47 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>HeavyGod</t>
+          <t>molodoy</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3.416</v>
+        <v>3.5331</v>
       </c>
       <c r="C23" t="n">
-        <v>1.3575</v>
+        <v>1.4041</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9308</v>
+        <v>0.9643</v>
       </c>
       <c r="E23" t="n">
-        <v>3.416</v>
+        <v>3.5331</v>
       </c>
       <c r="F23" t="n">
-        <v>3.416</v>
+        <v>1.1595</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>2.2668</v>
       </c>
       <c r="H23" t="n">
-        <v>4.7516</v>
+        <v>1.1595</v>
       </c>
       <c r="I23" t="n">
-        <v>4.7516</v>
+        <v>1.1894</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>2.2668</v>
       </c>
       <c r="K23" t="n">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="M23" t="n">
-        <v>4.7516</v>
+        <v>3.4562</v>
       </c>
       <c r="N23" t="n">
-        <v>276</v>
+        <v>391</v>
       </c>
     </row>
     <row r="24">
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3.1896</v>
+        <v>3.3276</v>
       </c>
       <c r="C24" t="n">
-        <v>1.2676</v>
+        <v>1.3224</v>
       </c>
       <c r="D24" t="n">
-        <v>0.8278</v>
+        <v>0.8725000000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>3.1896</v>
+        <v>3.3276</v>
       </c>
       <c r="F24" t="n">
-        <v>3.2877</v>
+        <v>3.2826</v>
       </c>
       <c r="G24" t="n">
         <v>-0.09810000000000001</v>
       </c>
       <c r="H24" t="n">
-        <v>4.4708</v>
+        <v>4.4596</v>
       </c>
       <c r="I24" t="n">
-        <v>4.586</v>
+        <v>4.5745</v>
       </c>
       <c r="J24" t="n">
         <v>-0.09810000000000001</v>
@@ -1541,7 +1541,7 @@
         <v>44</v>
       </c>
       <c r="M24" t="n">
-        <v>4.487900000000001</v>
+        <v>4.4764</v>
       </c>
       <c r="N24" t="n">
         <v>315</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.8434</v>
+        <v>2.876</v>
       </c>
       <c r="C25" t="n">
-        <v>1.13</v>
+        <v>1.1429</v>
       </c>
       <c r="D25" t="n">
-        <v>0.6702</v>
+        <v>0.6708</v>
       </c>
       <c r="E25" t="n">
-        <v>2.8434</v>
+        <v>2.876</v>
       </c>
       <c r="F25" t="n">
-        <v>2.4749</v>
+        <v>2.4618</v>
       </c>
       <c r="G25" t="n">
         <v>0.3685</v>
       </c>
       <c r="H25" t="n">
-        <v>2.6919</v>
+        <v>2.6631</v>
       </c>
       <c r="I25" t="n">
-        <v>2.6919</v>
+        <v>2.6631</v>
       </c>
       <c r="J25" t="n">
         <v>0.3685</v>
@@ -1587,7 +1587,7 @@
         <v>69</v>
       </c>
       <c r="M25" t="n">
-        <v>3.0604</v>
+        <v>3.0316</v>
       </c>
       <c r="N25" t="n">
         <v>245</v>
@@ -1596,47 +1596,47 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>jL</t>
+          <t>exit</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.8341</v>
+        <v>2.8653</v>
       </c>
       <c r="C26" t="n">
-        <v>1.1263</v>
+        <v>1.1387</v>
       </c>
       <c r="D26" t="n">
-        <v>0.6659</v>
+        <v>0.666</v>
       </c>
       <c r="E26" t="n">
-        <v>2.8341</v>
+        <v>2.8653</v>
       </c>
       <c r="F26" t="n">
-        <v>2.3492</v>
+        <v>2.5372</v>
       </c>
       <c r="G26" t="n">
-        <v>0.4849</v>
+        <v>0.2253</v>
       </c>
       <c r="H26" t="n">
-        <v>2.4167</v>
+        <v>2.8282</v>
       </c>
       <c r="I26" t="n">
-        <v>2.4167</v>
+        <v>2.9011</v>
       </c>
       <c r="J26" t="n">
-        <v>0.4849</v>
+        <v>0.2253</v>
       </c>
       <c r="K26" t="n">
-        <v>176</v>
+        <v>271</v>
       </c>
       <c r="L26" t="n">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="M26" t="n">
-        <v>2.9016</v>
+        <v>3.1264</v>
       </c>
       <c r="N26" t="n">
-        <v>245</v>
+        <v>315</v>
       </c>
     </row>
     <row r="27">
@@ -1646,16 +1646,16 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2.8011</v>
+        <v>2.8167</v>
       </c>
       <c r="C27" t="n">
-        <v>1.1132</v>
+        <v>1.1194</v>
       </c>
       <c r="D27" t="n">
-        <v>0.6509</v>
+        <v>0.6443</v>
       </c>
       <c r="E27" t="n">
-        <v>2.8011</v>
+        <v>2.8167</v>
       </c>
       <c r="F27" t="n">
         <v>2.8011</v>
@@ -1688,599 +1688,599 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>exit</t>
+          <t>jL</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.7584</v>
+        <v>2.8107</v>
       </c>
       <c r="C28" t="n">
-        <v>1.0962</v>
+        <v>1.117</v>
       </c>
       <c r="D28" t="n">
-        <v>0.6315</v>
+        <v>0.6417</v>
       </c>
       <c r="E28" t="n">
-        <v>2.7584</v>
+        <v>2.8107</v>
       </c>
       <c r="F28" t="n">
-        <v>2.5331</v>
+        <v>2.3493</v>
       </c>
       <c r="G28" t="n">
-        <v>0.2253</v>
+        <v>0.4849</v>
       </c>
       <c r="H28" t="n">
-        <v>2.8193</v>
+        <v>2.417</v>
       </c>
       <c r="I28" t="n">
-        <v>2.8919</v>
+        <v>2.417</v>
       </c>
       <c r="J28" t="n">
-        <v>0.2253</v>
+        <v>0.4849</v>
       </c>
       <c r="K28" t="n">
-        <v>271</v>
+        <v>176</v>
       </c>
       <c r="L28" t="n">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="M28" t="n">
-        <v>3.1172</v>
+        <v>2.9019</v>
       </c>
       <c r="N28" t="n">
-        <v>315</v>
+        <v>245</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>dgt</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2.4267</v>
+        <v>2.6308</v>
       </c>
       <c r="C29" t="n">
-        <v>0.9644</v>
+        <v>1.0455</v>
       </c>
       <c r="D29" t="n">
-        <v>0.4805</v>
+        <v>0.5613</v>
       </c>
       <c r="E29" t="n">
-        <v>2.4267</v>
+        <v>2.6308</v>
       </c>
       <c r="F29" t="n">
-        <v>2.5167</v>
+        <v>2.2308</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.09</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>2.7833</v>
+        <v>2.2308</v>
       </c>
       <c r="I29" t="n">
-        <v>2.855</v>
+        <v>2.2308</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.09</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>285</v>
+        <v>88</v>
       </c>
       <c r="L29" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>2.765</v>
+        <v>2.2308</v>
       </c>
       <c r="N29" t="n">
-        <v>391</v>
+        <v>88</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>mizu</t>
+          <t>Lake</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2.4235</v>
+        <v>2.5313</v>
       </c>
       <c r="C30" t="n">
-        <v>0.9631</v>
+        <v>1.006</v>
       </c>
       <c r="D30" t="n">
-        <v>0.479</v>
+        <v>0.5169</v>
       </c>
       <c r="E30" t="n">
-        <v>2.4235</v>
+        <v>2.5313</v>
       </c>
       <c r="F30" t="n">
-        <v>2.4235</v>
+        <v>2.3157</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>2.5794</v>
+        <v>2.3434</v>
       </c>
       <c r="I30" t="n">
-        <v>2.5794</v>
+        <v>2.3434</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>197</v>
+        <v>172</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>2.5794</v>
+        <v>2.3434</v>
       </c>
       <c r="N30" t="n">
-        <v>197</v>
+        <v>172</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lake</t>
+          <t>mizu</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2.3181</v>
+        <v>2.4741</v>
       </c>
       <c r="C31" t="n">
-        <v>0.9212</v>
+        <v>0.9832</v>
       </c>
       <c r="D31" t="n">
-        <v>0.431</v>
+        <v>0.4913</v>
       </c>
       <c r="E31" t="n">
-        <v>2.3181</v>
+        <v>2.4741</v>
       </c>
       <c r="F31" t="n">
-        <v>2.3181</v>
+        <v>2.4319</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>2.3486</v>
+        <v>2.5977</v>
       </c>
       <c r="I31" t="n">
-        <v>2.3486</v>
+        <v>2.5977</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>172</v>
+        <v>197</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>2.3486</v>
+        <v>2.5977</v>
       </c>
       <c r="N31" t="n">
-        <v>172</v>
+        <v>197</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>fame</t>
+          <t>hyped</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2.2768</v>
+        <v>2.3846</v>
       </c>
       <c r="C32" t="n">
-        <v>0.9048</v>
+        <v>0.9477</v>
       </c>
       <c r="D32" t="n">
-        <v>0.4122</v>
+        <v>0.4513</v>
       </c>
       <c r="E32" t="n">
-        <v>2.2768</v>
+        <v>2.3846</v>
       </c>
       <c r="F32" t="n">
-        <v>2.2768</v>
+        <v>2.134</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>2.2768</v>
+        <v>2.134</v>
       </c>
       <c r="I32" t="n">
-        <v>2.3355</v>
+        <v>2.134</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>315</v>
+        <v>188</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>2.3355</v>
+        <v>2.134</v>
       </c>
       <c r="N32" t="n">
-        <v>315</v>
+        <v>188</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>dgt</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2.2313</v>
+        <v>2.3822</v>
       </c>
       <c r="C33" t="n">
-        <v>0.8867</v>
+        <v>0.9467</v>
       </c>
       <c r="D33" t="n">
-        <v>0.3915</v>
+        <v>0.4503</v>
       </c>
       <c r="E33" t="n">
-        <v>2.2313</v>
+        <v>2.3822</v>
       </c>
       <c r="F33" t="n">
-        <v>2.2313</v>
+        <v>2.5107</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>-0.09</v>
       </c>
       <c r="H33" t="n">
-        <v>2.2313</v>
+        <v>2.7703</v>
       </c>
       <c r="I33" t="n">
-        <v>2.2313</v>
+        <v>2.8417</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>-0.09</v>
       </c>
       <c r="K33" t="n">
-        <v>88</v>
+        <v>285</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="M33" t="n">
-        <v>2.2313</v>
+        <v>2.7517</v>
       </c>
       <c r="N33" t="n">
-        <v>88</v>
+        <v>391</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>hyped</t>
+          <t>fame</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2.134</v>
+        <v>2.3223</v>
       </c>
       <c r="C34" t="n">
-        <v>0.8481</v>
+        <v>0.9229000000000001</v>
       </c>
       <c r="D34" t="n">
-        <v>0.3472</v>
+        <v>0.4235</v>
       </c>
       <c r="E34" t="n">
-        <v>2.134</v>
+        <v>2.3223</v>
       </c>
       <c r="F34" t="n">
-        <v>2.134</v>
+        <v>2.2866</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>2.134</v>
+        <v>2.2866</v>
       </c>
       <c r="I34" t="n">
-        <v>2.134</v>
+        <v>2.3455</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>188</v>
+        <v>315</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>2.134</v>
+        <v>2.3455</v>
       </c>
       <c r="N34" t="n">
-        <v>188</v>
+        <v>315</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>kade0</t>
+          <t>Tauson</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2.0995</v>
+        <v>2.1955</v>
       </c>
       <c r="C35" t="n">
-        <v>0.8344</v>
+        <v>0.8725000000000001</v>
       </c>
       <c r="D35" t="n">
-        <v>0.3315</v>
+        <v>0.3669</v>
       </c>
       <c r="E35" t="n">
-        <v>2.0995</v>
+        <v>2.1955</v>
       </c>
       <c r="F35" t="n">
-        <v>2.0995</v>
+        <v>1.9805</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>2.0995</v>
+        <v>1.9805</v>
       </c>
       <c r="I35" t="n">
-        <v>2.0995</v>
+        <v>1.9805</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>197</v>
+        <v>153</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>2.0995</v>
+        <v>1.9805</v>
       </c>
       <c r="N35" t="n">
-        <v>197</v>
+        <v>153</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>b1t</t>
+          <t>kade0</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2.0745</v>
+        <v>2.092</v>
       </c>
       <c r="C36" t="n">
-        <v>0.8244</v>
+        <v>0.8314</v>
       </c>
       <c r="D36" t="n">
-        <v>0.3202</v>
+        <v>0.3206</v>
       </c>
       <c r="E36" t="n">
-        <v>2.0745</v>
+        <v>2.092</v>
       </c>
       <c r="F36" t="n">
-        <v>2.5812</v>
+        <v>2.1083</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.5067</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>2.9246</v>
+        <v>2.1083</v>
       </c>
       <c r="I36" t="n">
-        <v>2.9246</v>
+        <v>2.1083</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.5067</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>176</v>
+        <v>197</v>
       </c>
       <c r="L36" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>2.4179</v>
+        <v>2.1083</v>
       </c>
       <c r="N36" t="n">
-        <v>245</v>
+        <v>197</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Techno</t>
+          <t>pancc</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1.9861</v>
+        <v>1.9568</v>
       </c>
       <c r="C37" t="n">
-        <v>0.7893</v>
+        <v>0.7776</v>
       </c>
       <c r="D37" t="n">
-        <v>0.2799</v>
+        <v>0.2602</v>
       </c>
       <c r="E37" t="n">
-        <v>1.9861</v>
+        <v>1.9568</v>
       </c>
       <c r="F37" t="n">
-        <v>2.807</v>
+        <v>1.7941</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.8209</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>3.4188</v>
+        <v>1.7941</v>
       </c>
       <c r="I37" t="n">
-        <v>3.4188</v>
+        <v>1.7941</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.8209</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>144</v>
+        <v>240</v>
       </c>
       <c r="L37" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>2.5979</v>
+        <v>1.7941</v>
       </c>
       <c r="N37" t="n">
-        <v>192</v>
+        <v>240</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Tauson</t>
+          <t>biguzera</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1.9815</v>
+        <v>1.9233</v>
       </c>
       <c r="C38" t="n">
-        <v>0.7875</v>
+        <v>0.7643</v>
       </c>
       <c r="D38" t="n">
-        <v>0.2778</v>
+        <v>0.2453</v>
       </c>
       <c r="E38" t="n">
-        <v>1.9815</v>
+        <v>1.9233</v>
       </c>
       <c r="F38" t="n">
-        <v>1.9815</v>
+        <v>1.8953</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>1.9815</v>
+        <v>1.8953</v>
       </c>
       <c r="I38" t="n">
-        <v>1.9815</v>
+        <v>1.8953</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>1.9815</v>
+        <v>1.8953</v>
       </c>
       <c r="N38" t="n">
-        <v>153</v>
+        <v>165</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>biguzera</t>
+          <t>b1t</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1.8761</v>
+        <v>1.914</v>
       </c>
       <c r="C39" t="n">
-        <v>0.7456</v>
+        <v>0.7606000000000001</v>
       </c>
       <c r="D39" t="n">
-        <v>0.2298</v>
+        <v>0.2411</v>
       </c>
       <c r="E39" t="n">
-        <v>1.8761</v>
+        <v>1.914</v>
       </c>
       <c r="F39" t="n">
-        <v>1.8761</v>
+        <v>2.5814</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>-0.5067</v>
       </c>
       <c r="H39" t="n">
-        <v>1.8761</v>
+        <v>2.9249</v>
       </c>
       <c r="I39" t="n">
-        <v>1.8761</v>
+        <v>2.9249</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>-0.5067</v>
       </c>
       <c r="K39" t="n">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="M39" t="n">
-        <v>1.8761</v>
+        <v>2.4182</v>
       </c>
       <c r="N39" t="n">
-        <v>165</v>
+        <v>245</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>pancc</t>
+          <t>Techno</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1.7941</v>
+        <v>1.8788</v>
       </c>
       <c r="C40" t="n">
-        <v>0.713</v>
+        <v>0.7466</v>
       </c>
       <c r="D40" t="n">
-        <v>0.1925</v>
+        <v>0.2254</v>
       </c>
       <c r="E40" t="n">
-        <v>1.7941</v>
+        <v>1.8788</v>
       </c>
       <c r="F40" t="n">
-        <v>1.7941</v>
+        <v>2.8071</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>-0.8209</v>
       </c>
       <c r="H40" t="n">
-        <v>1.7941</v>
+        <v>3.4189</v>
       </c>
       <c r="I40" t="n">
-        <v>1.7941</v>
+        <v>3.4189</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>-0.8209</v>
       </c>
       <c r="K40" t="n">
-        <v>240</v>
+        <v>144</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="M40" t="n">
-        <v>1.7941</v>
+        <v>2.598</v>
       </c>
       <c r="N40" t="n">
-        <v>240</v>
+        <v>192</v>
       </c>
     </row>
     <row r="41">
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1.7279</v>
+        <v>1.8296</v>
       </c>
       <c r="C41" t="n">
-        <v>0.6867</v>
+        <v>0.7271</v>
       </c>
       <c r="D41" t="n">
-        <v>0.1624</v>
+        <v>0.2034</v>
       </c>
       <c r="E41" t="n">
-        <v>1.7279</v>
+        <v>1.8296</v>
       </c>
       <c r="F41" t="n">
-        <v>1.7279</v>
+        <v>1.7258</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>1.7279</v>
+        <v>1.7258</v>
       </c>
       <c r="I41" t="n">
-        <v>1.7279</v>
+        <v>1.7258</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>1.7279</v>
+        <v>1.7258</v>
       </c>
       <c r="N41" t="n">
         <v>153</v>
@@ -2336,28 +2336,28 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1.6101</v>
+        <v>1.7227</v>
       </c>
       <c r="C42" t="n">
-        <v>0.6399</v>
+        <v>0.6846</v>
       </c>
       <c r="D42" t="n">
-        <v>0.1087</v>
+        <v>0.1557</v>
       </c>
       <c r="E42" t="n">
-        <v>1.6101</v>
+        <v>1.7227</v>
       </c>
       <c r="F42" t="n">
-        <v>1.6101</v>
+        <v>1.6098</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>1.6101</v>
+        <v>1.6098</v>
       </c>
       <c r="I42" t="n">
-        <v>1.6101</v>
+        <v>1.6098</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -2369,7 +2369,7 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>1.6101</v>
+        <v>1.6098</v>
       </c>
       <c r="N42" t="n">
         <v>197</v>
@@ -2378,139 +2378,139 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>arrozdoce</t>
+          <t>hades</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1.6001</v>
+        <v>1.6081</v>
       </c>
       <c r="C43" t="n">
-        <v>0.6359</v>
+        <v>0.6391</v>
       </c>
       <c r="D43" t="n">
-        <v>0.1042</v>
+        <v>0.1045</v>
       </c>
       <c r="E43" t="n">
-        <v>1.6001</v>
+        <v>1.6081</v>
       </c>
       <c r="F43" t="n">
-        <v>1.4247</v>
+        <v>1.4574</v>
       </c>
       <c r="G43" t="n">
-        <v>0.1754</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>1.4247</v>
+        <v>1.4574</v>
       </c>
       <c r="I43" t="n">
-        <v>1.4614</v>
+        <v>1.4574</v>
       </c>
       <c r="J43" t="n">
-        <v>0.1754</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="L43" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>1.6368</v>
+        <v>1.4574</v>
       </c>
       <c r="N43" t="n">
-        <v>311</v>
+        <v>276</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ICY</t>
+          <t>arrozdoce</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1.5138</v>
+        <v>1.539</v>
       </c>
       <c r="C44" t="n">
-        <v>0.6016</v>
+        <v>0.6116</v>
       </c>
       <c r="D44" t="n">
-        <v>0.0649</v>
+        <v>0.0736</v>
       </c>
       <c r="E44" t="n">
-        <v>1.5138</v>
+        <v>1.539</v>
       </c>
       <c r="F44" t="n">
-        <v>1.5138</v>
+        <v>1.424</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>0.1752</v>
       </c>
       <c r="H44" t="n">
-        <v>1.5138</v>
+        <v>1.424</v>
       </c>
       <c r="I44" t="n">
-        <v>1.5528</v>
+        <v>1.4607</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>0.1752</v>
       </c>
       <c r="K44" t="n">
-        <v>315</v>
+        <v>266</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="M44" t="n">
-        <v>1.5528</v>
+        <v>1.6359</v>
       </c>
       <c r="N44" t="n">
-        <v>315</v>
+        <v>311</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>hades</t>
+          <t>ICY</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1.4568</v>
+        <v>1.509</v>
       </c>
       <c r="C45" t="n">
-        <v>0.5789</v>
+        <v>0.5997</v>
       </c>
       <c r="D45" t="n">
-        <v>0.039</v>
+        <v>0.0602</v>
       </c>
       <c r="E45" t="n">
-        <v>1.4568</v>
+        <v>1.509</v>
       </c>
       <c r="F45" t="n">
-        <v>1.4568</v>
+        <v>1.5012</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>1.4568</v>
+        <v>1.5012</v>
       </c>
       <c r="I45" t="n">
-        <v>1.4568</v>
+        <v>1.5399</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>276</v>
+        <v>315</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>1.4568</v>
+        <v>1.5399</v>
       </c>
       <c r="N45" t="n">
-        <v>276</v>
+        <v>315</v>
       </c>
     </row>
     <row r="46">
@@ -2520,31 +2520,31 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1.4374</v>
+        <v>1.3245</v>
       </c>
       <c r="C46" t="n">
-        <v>0.5712</v>
+        <v>0.5264</v>
       </c>
       <c r="D46" t="n">
-        <v>0.0301</v>
+        <v>-0.0222</v>
       </c>
       <c r="E46" t="n">
-        <v>1.4374</v>
+        <v>1.3245</v>
       </c>
       <c r="F46" t="n">
-        <v>1.7797</v>
+        <v>1.7794</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.3423</v>
+        <v>-0.3428</v>
       </c>
       <c r="H46" t="n">
-        <v>1.7797</v>
+        <v>1.7794</v>
       </c>
       <c r="I46" t="n">
-        <v>1.7797</v>
+        <v>1.7794</v>
       </c>
       <c r="J46" t="n">
-        <v>-0.3423</v>
+        <v>-0.3428</v>
       </c>
       <c r="K46" t="n">
         <v>214</v>
@@ -2553,7 +2553,7 @@
         <v>218</v>
       </c>
       <c r="M46" t="n">
-        <v>1.4374</v>
+        <v>1.4366</v>
       </c>
       <c r="N46" t="n">
         <v>432</v>
@@ -2566,28 +2566,28 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1.3657</v>
+        <v>1.2196</v>
       </c>
       <c r="C47" t="n">
-        <v>0.5427</v>
+        <v>0.4847</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.0025</v>
+        <v>-0.06909999999999999</v>
       </c>
       <c r="E47" t="n">
-        <v>1.3657</v>
+        <v>1.2196</v>
       </c>
       <c r="F47" t="n">
-        <v>1.3657</v>
+        <v>1.3367</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>1.3657</v>
+        <v>1.3367</v>
       </c>
       <c r="I47" t="n">
-        <v>1.3657</v>
+        <v>1.3367</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -2599,7 +2599,7 @@
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>1.3657</v>
+        <v>1.3367</v>
       </c>
       <c r="N47" t="n">
         <v>172</v>
@@ -2612,28 +2612,28 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1.2934</v>
+        <v>1.0672</v>
       </c>
       <c r="C48" t="n">
-        <v>0.514</v>
+        <v>0.4241</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.0354</v>
+        <v>-0.1371</v>
       </c>
       <c r="E48" t="n">
-        <v>1.2934</v>
+        <v>1.0672</v>
       </c>
       <c r="F48" t="n">
-        <v>1.2934</v>
+        <v>1.2926</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>1.2934</v>
+        <v>1.2926</v>
       </c>
       <c r="I48" t="n">
-        <v>1.2934</v>
+        <v>1.2926</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -2645,7 +2645,7 @@
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>1.2934</v>
+        <v>1.2926</v>
       </c>
       <c r="N48" t="n">
         <v>197</v>
@@ -2658,28 +2658,28 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1.1496</v>
+        <v>1.0381</v>
       </c>
       <c r="C49" t="n">
-        <v>0.4569</v>
+        <v>0.4125</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.1009</v>
+        <v>-0.1501</v>
       </c>
       <c r="E49" t="n">
-        <v>1.1496</v>
+        <v>1.0381</v>
       </c>
       <c r="F49" t="n">
-        <v>0.6247</v>
+        <v>0.6251</v>
       </c>
       <c r="G49" t="n">
         <v>0.5249</v>
       </c>
       <c r="H49" t="n">
-        <v>0.6247</v>
+        <v>0.6251</v>
       </c>
       <c r="I49" t="n">
-        <v>0.6247</v>
+        <v>0.6251</v>
       </c>
       <c r="J49" t="n">
         <v>0.5249</v>
@@ -2691,7 +2691,7 @@
         <v>48</v>
       </c>
       <c r="M49" t="n">
-        <v>1.1496</v>
+        <v>1.15</v>
       </c>
       <c r="N49" t="n">
         <v>192</v>
@@ -2704,28 +2704,28 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.9927</v>
+        <v>0.9466</v>
       </c>
       <c r="C50" t="n">
-        <v>0.3945</v>
+        <v>0.3762</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.1723</v>
+        <v>-0.191</v>
       </c>
       <c r="E50" t="n">
-        <v>0.9927</v>
+        <v>0.9466</v>
       </c>
       <c r="F50" t="n">
-        <v>0.9927</v>
+        <v>0.9727</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>0.9927</v>
+        <v>0.9727</v>
       </c>
       <c r="I50" t="n">
-        <v>0.9927</v>
+        <v>0.9727</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -2737,7 +2737,7 @@
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>0.9927</v>
+        <v>0.9727</v>
       </c>
       <c r="N50" t="n">
         <v>240</v>
@@ -2750,28 +2750,28 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.7917</v>
+        <v>0.778</v>
       </c>
       <c r="C51" t="n">
-        <v>0.3146</v>
+        <v>0.3092</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.2638</v>
+        <v>-0.2663</v>
       </c>
       <c r="E51" t="n">
-        <v>0.7917</v>
+        <v>0.778</v>
       </c>
       <c r="F51" t="n">
-        <v>0.7917</v>
+        <v>0.7891</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>0.7917</v>
+        <v>0.7891</v>
       </c>
       <c r="I51" t="n">
-        <v>0.8121</v>
+        <v>0.8094</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -2783,7 +2783,7 @@
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>0.8121</v>
+        <v>0.8094</v>
       </c>
       <c r="N51" t="n">
         <v>315</v>
@@ -2792,277 +2792,277 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>FL4MUS</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.7796999999999999</v>
+        <v>0.6728</v>
       </c>
       <c r="C52" t="n">
-        <v>0.3099</v>
+        <v>0.2674</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.2693</v>
+        <v>-0.3133</v>
       </c>
       <c r="E52" t="n">
-        <v>0.7796999999999999</v>
+        <v>0.6728</v>
       </c>
       <c r="F52" t="n">
-        <v>0.7796999999999999</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>0.7796999999999999</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="I52" t="n">
-        <v>0.7998</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>315</v>
+        <v>153</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>0.7998</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="N52" t="n">
-        <v>315</v>
+        <v>153</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>FL4MUS</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.6556</v>
+        <v>0.5857</v>
       </c>
       <c r="C53" t="n">
-        <v>0.2605</v>
+        <v>0.2328</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.3258</v>
+        <v>-0.3522</v>
       </c>
       <c r="E53" t="n">
-        <v>0.6556</v>
+        <v>0.5857</v>
       </c>
       <c r="F53" t="n">
-        <v>0.6556</v>
+        <v>0.7874</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>0.6556</v>
+        <v>0.7874</v>
       </c>
       <c r="I53" t="n">
-        <v>0.6556</v>
+        <v>0.8077</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>153</v>
+        <v>315</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>0.6556</v>
+        <v>0.8077</v>
       </c>
       <c r="N53" t="n">
-        <v>153</v>
+        <v>315</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>bLitz</t>
+          <t>saffee</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.622</v>
+        <v>0.5804</v>
       </c>
       <c r="C54" t="n">
-        <v>0.2472</v>
+        <v>0.2307</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.3411</v>
+        <v>-0.3546</v>
       </c>
       <c r="E54" t="n">
-        <v>0.622</v>
+        <v>0.5804</v>
       </c>
       <c r="F54" t="n">
-        <v>0.5193</v>
+        <v>1.3003</v>
       </c>
       <c r="G54" t="n">
-        <v>0.1027</v>
+        <v>-0.7756</v>
       </c>
       <c r="H54" t="n">
-        <v>0.5193</v>
+        <v>1.3003</v>
       </c>
       <c r="I54" t="n">
-        <v>0.5193</v>
+        <v>1.3338</v>
       </c>
       <c r="J54" t="n">
-        <v>0.1027</v>
+        <v>-0.7756</v>
       </c>
       <c r="K54" t="n">
-        <v>144</v>
+        <v>271</v>
       </c>
       <c r="L54" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="M54" t="n">
-        <v>0.622</v>
+        <v>0.5582000000000001</v>
       </c>
       <c r="N54" t="n">
-        <v>192</v>
+        <v>315</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>jottAAA</t>
+          <t>youka</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.6014</v>
+        <v>0.5648</v>
       </c>
       <c r="C55" t="n">
-        <v>0.239</v>
+        <v>0.2245</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.3504</v>
+        <v>-0.3615</v>
       </c>
       <c r="E55" t="n">
-        <v>0.6014</v>
+        <v>0.5648</v>
       </c>
       <c r="F55" t="n">
-        <v>1.901</v>
+        <v>0.5933</v>
       </c>
       <c r="G55" t="n">
-        <v>-1.2996</v>
+        <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>1.901</v>
+        <v>0.5933</v>
       </c>
       <c r="I55" t="n">
-        <v>1.95</v>
+        <v>0.5933</v>
       </c>
       <c r="J55" t="n">
-        <v>-1.2996</v>
+        <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>356</v>
+        <v>197</v>
       </c>
       <c r="L55" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>0.6503999999999999</v>
+        <v>0.5933</v>
       </c>
       <c r="N55" t="n">
-        <v>465</v>
+        <v>197</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>youka</t>
+          <t>bLitz</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.5937</v>
+        <v>0.5552</v>
       </c>
       <c r="C56" t="n">
-        <v>0.2359</v>
+        <v>0.2206</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.3539</v>
+        <v>-0.3658</v>
       </c>
       <c r="E56" t="n">
-        <v>0.5937</v>
+        <v>0.5552</v>
       </c>
       <c r="F56" t="n">
-        <v>0.5937</v>
+        <v>0.5198</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>0.1027</v>
       </c>
       <c r="H56" t="n">
-        <v>0.5937</v>
+        <v>0.5198</v>
       </c>
       <c r="I56" t="n">
-        <v>0.5937</v>
+        <v>0.5198</v>
       </c>
       <c r="J56" t="n">
-        <v>0</v>
+        <v>0.1027</v>
       </c>
       <c r="K56" t="n">
-        <v>197</v>
+        <v>144</v>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="M56" t="n">
-        <v>0.5937</v>
+        <v>0.6225000000000001</v>
       </c>
       <c r="N56" t="n">
-        <v>197</v>
+        <v>192</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>saffee</t>
+          <t>jottAAA</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.5105</v>
+        <v>0.5367</v>
       </c>
       <c r="C57" t="n">
-        <v>0.2029</v>
+        <v>0.2133</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.3918</v>
+        <v>-0.3741</v>
       </c>
       <c r="E57" t="n">
-        <v>0.5105</v>
+        <v>0.5367</v>
       </c>
       <c r="F57" t="n">
-        <v>1.2861</v>
+        <v>1.9008</v>
       </c>
       <c r="G57" t="n">
-        <v>-0.7756</v>
+        <v>-1.3</v>
       </c>
       <c r="H57" t="n">
-        <v>1.2861</v>
+        <v>1.9008</v>
       </c>
       <c r="I57" t="n">
-        <v>1.3192</v>
+        <v>1.9498</v>
       </c>
       <c r="J57" t="n">
-        <v>-0.7756</v>
+        <v>-1.3</v>
       </c>
       <c r="K57" t="n">
-        <v>271</v>
+        <v>356</v>
       </c>
       <c r="L57" t="n">
-        <v>44</v>
+        <v>109</v>
       </c>
       <c r="M57" t="n">
-        <v>0.5436</v>
+        <v>0.6497999999999999</v>
       </c>
       <c r="N57" t="n">
-        <v>315</v>
+        <v>465</v>
       </c>
     </row>
     <row r="58">
@@ -3072,28 +3072,28 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.4227</v>
+        <v>0.366</v>
       </c>
       <c r="C58" t="n">
-        <v>0.168</v>
+        <v>0.1455</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.4318</v>
+        <v>-0.4503</v>
       </c>
       <c r="E58" t="n">
-        <v>0.4227</v>
+        <v>0.366</v>
       </c>
       <c r="F58" t="n">
-        <v>0.4227</v>
+        <v>0.4231</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>0.4227</v>
+        <v>0.4231</v>
       </c>
       <c r="I58" t="n">
-        <v>0.4227</v>
+        <v>0.4231</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -3105,7 +3105,7 @@
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>0.4227</v>
+        <v>0.4231</v>
       </c>
       <c r="N58" t="n">
         <v>165</v>
@@ -3118,28 +3118,28 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.4096</v>
+        <v>0.2103</v>
       </c>
       <c r="C59" t="n">
-        <v>0.1628</v>
+        <v>0.08359999999999999</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.4377</v>
+        <v>-0.5199</v>
       </c>
       <c r="E59" t="n">
-        <v>0.4096</v>
+        <v>0.2103</v>
       </c>
       <c r="F59" t="n">
-        <v>0.9876</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G59" t="n">
         <v>-0.578</v>
       </c>
       <c r="H59" t="n">
-        <v>0.9876</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I59" t="n">
-        <v>0.9876</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="J59" t="n">
         <v>-0.578</v>
@@ -3151,7 +3151,7 @@
         <v>48</v>
       </c>
       <c r="M59" t="n">
-        <v>0.4096000000000001</v>
+        <v>0.362</v>
       </c>
       <c r="N59" t="n">
         <v>192</v>
@@ -3164,28 +3164,28 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.2</v>
+        <v>0.0556</v>
       </c>
       <c r="C60" t="n">
-        <v>0.0795</v>
+        <v>0.0221</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.5332</v>
+        <v>-0.589</v>
       </c>
       <c r="E60" t="n">
-        <v>0.2</v>
+        <v>0.0556</v>
       </c>
       <c r="F60" t="n">
-        <v>0.2</v>
+        <v>0.2001</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>0.2</v>
+        <v>0.2001</v>
       </c>
       <c r="I60" t="n">
-        <v>0.2</v>
+        <v>0.2001</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -3197,7 +3197,7 @@
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>0.2</v>
+        <v>0.2001</v>
       </c>
       <c r="N60" t="n">
         <v>165</v>
@@ -3210,28 +3210,28 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.1842</v>
+        <v>0.0502</v>
       </c>
       <c r="C61" t="n">
-        <v>0.0732</v>
+        <v>0.0199</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.5404</v>
+        <v>-0.5914</v>
       </c>
       <c r="E61" t="n">
-        <v>0.1842</v>
+        <v>0.0502</v>
       </c>
       <c r="F61" t="n">
-        <v>1.1477</v>
+        <v>1.1564</v>
       </c>
       <c r="G61" t="n">
         <v>-0.9635</v>
       </c>
       <c r="H61" t="n">
-        <v>1.1477</v>
+        <v>1.1564</v>
       </c>
       <c r="I61" t="n">
-        <v>1.1773</v>
+        <v>1.1862</v>
       </c>
       <c r="J61" t="n">
         <v>-0.9635</v>
@@ -3243,7 +3243,7 @@
         <v>44</v>
       </c>
       <c r="M61" t="n">
-        <v>0.2138</v>
+        <v>0.2226999999999999</v>
       </c>
       <c r="N61" t="n">
         <v>315</v>
@@ -3256,16 +3256,16 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.09370000000000001</v>
+        <v>-0.0478</v>
       </c>
       <c r="C62" t="n">
-        <v>0.0372</v>
+        <v>-0.019</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.5815</v>
+        <v>-0.6352</v>
       </c>
       <c r="E62" t="n">
-        <v>0.09370000000000001</v>
+        <v>-0.0478</v>
       </c>
       <c r="F62" t="n">
         <v>0.09370000000000001</v>
@@ -3298,47 +3298,47 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>magixx</t>
+          <t>jabbi</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.0551</v>
+        <v>-0.1157</v>
       </c>
       <c r="C63" t="n">
-        <v>0.0219</v>
+        <v>-0.046</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.5991</v>
+        <v>-0.6655</v>
       </c>
       <c r="E63" t="n">
-        <v>0.0551</v>
+        <v>-0.1157</v>
       </c>
       <c r="F63" t="n">
-        <v>0.0145</v>
+        <v>-1.3261</v>
       </c>
       <c r="G63" t="n">
-        <v>0.0406</v>
+        <v>1.2728</v>
       </c>
       <c r="H63" t="n">
-        <v>0.0145</v>
+        <v>-1.3261</v>
       </c>
       <c r="I63" t="n">
-        <v>0.0145</v>
+        <v>-1.3261</v>
       </c>
       <c r="J63" t="n">
-        <v>0.0406</v>
+        <v>1.2728</v>
       </c>
       <c r="K63" t="n">
-        <v>132</v>
+        <v>214</v>
       </c>
       <c r="L63" t="n">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="M63" t="n">
-        <v>0.0551</v>
+        <v>-0.05330000000000013</v>
       </c>
       <c r="N63" t="n">
-        <v>327</v>
+        <v>432</v>
       </c>
     </row>
     <row r="64">
@@ -3348,16 +3348,16 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.0514</v>
+        <v>-0.1205</v>
       </c>
       <c r="C64" t="n">
-        <v>0.0204</v>
+        <v>-0.0479</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.6008</v>
+        <v>-0.6676</v>
       </c>
       <c r="E64" t="n">
-        <v>0.0514</v>
+        <v>-0.1205</v>
       </c>
       <c r="F64" t="n">
         <v>0.0514</v>
@@ -3390,47 +3390,47 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>jabbi</t>
+          <t>magixx</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.0525</v>
+        <v>-0.2232</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.0209</v>
+        <v>-0.0887</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.6481</v>
+        <v>-0.7135</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.0525</v>
+        <v>-0.2232</v>
       </c>
       <c r="F65" t="n">
-        <v>-1.3259</v>
+        <v>0.0145</v>
       </c>
       <c r="G65" t="n">
-        <v>1.2734</v>
+        <v>0.0406</v>
       </c>
       <c r="H65" t="n">
-        <v>-1.3259</v>
+        <v>0.0145</v>
       </c>
       <c r="I65" t="n">
-        <v>-1.3259</v>
+        <v>0.0145</v>
       </c>
       <c r="J65" t="n">
-        <v>1.2734</v>
+        <v>0.0406</v>
       </c>
       <c r="K65" t="n">
-        <v>214</v>
+        <v>132</v>
       </c>
       <c r="L65" t="n">
-        <v>218</v>
+        <v>195</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.05249999999999999</v>
+        <v>0.0551</v>
       </c>
       <c r="N65" t="n">
-        <v>432</v>
+        <v>327</v>
       </c>
     </row>
     <row r="66">
@@ -3440,28 +3440,28 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.2931</v>
+        <v>-0.3797</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.1165</v>
+        <v>-0.1509</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.7576000000000001</v>
+        <v>-0.7834</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.2931</v>
+        <v>-0.3797</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.2931</v>
+        <v>-0.3015</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.2931</v>
+        <v>-0.3015</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.2931</v>
+        <v>-0.3015</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -3473,7 +3473,7 @@
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>-0.2931</v>
+        <v>-0.3015</v>
       </c>
       <c r="N66" t="n">
         <v>172</v>
@@ -3486,16 +3486,16 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.648</v>
+        <v>-0.7601</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.2575</v>
+        <v>-0.3021</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.9192</v>
+        <v>-0.9533</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.648</v>
+        <v>-0.7601</v>
       </c>
       <c r="F67" t="n">
         <v>-0.648</v>
@@ -3528,231 +3528,231 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>slaxz-</t>
+          <t>Snax</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-0.7413</v>
+        <v>-0.9123</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.2946</v>
+        <v>-0.3626</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.9617</v>
+        <v>-1.0213</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.7413</v>
+        <v>-0.9123</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.7413</v>
+        <v>-0.7514</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.7413</v>
+        <v>-0.7514</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.7413</v>
+        <v>-0.7514</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>172</v>
+        <v>276</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>-0.7413</v>
+        <v>-0.7514</v>
       </c>
       <c r="N68" t="n">
-        <v>172</v>
+        <v>276</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Snax</t>
+          <t>ewjerkz</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-0.7517</v>
+        <v>-1.0136</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.2987</v>
+        <v>-0.4028</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.9664</v>
+        <v>-1.0666</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.7517</v>
+        <v>-1.0136</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.7517</v>
+        <v>-0.1047</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>-0.7581</v>
       </c>
       <c r="H69" t="n">
-        <v>-0.7517</v>
+        <v>-0.1047</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.7517</v>
+        <v>-0.1074</v>
       </c>
       <c r="J69" t="n">
-        <v>0</v>
+        <v>-0.7581</v>
       </c>
       <c r="K69" t="n">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="M69" t="n">
-        <v>-0.7517</v>
+        <v>-0.8654999999999999</v>
       </c>
       <c r="N69" t="n">
-        <v>276</v>
+        <v>311</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ewjerkz</t>
+          <t>slaxz-</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-0.8796</v>
+        <v>-1.0565</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.3496</v>
+        <v>-0.4199</v>
       </c>
       <c r="D70" t="n">
-        <v>-1.0246</v>
+        <v>-1.0857</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.8796</v>
+        <v>-1.0565</v>
       </c>
       <c r="F70" t="n">
-        <v>-0.1217</v>
+        <v>-0.7506</v>
       </c>
       <c r="G70" t="n">
-        <v>-0.7579</v>
+        <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>-0.1217</v>
+        <v>-0.7506</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.1248</v>
+        <v>-0.7506</v>
       </c>
       <c r="J70" t="n">
-        <v>-0.7579</v>
+        <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>266</v>
+        <v>172</v>
       </c>
       <c r="L70" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>-0.8827</v>
+        <v>-0.7506</v>
       </c>
       <c r="N70" t="n">
-        <v>311</v>
+        <v>172</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>reck</t>
+          <t>ztr</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-0.9232</v>
+        <v>-1.1129</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.3669</v>
+        <v>-0.4423</v>
       </c>
       <c r="D71" t="n">
-        <v>-1.0445</v>
+        <v>-1.1109</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.9232</v>
+        <v>-1.1129</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.9232</v>
+        <v>-1.0488</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>-0.9232</v>
+        <v>-1.0488</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.9232</v>
+        <v>-1.0488</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>172</v>
+        <v>153</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>-0.9232</v>
+        <v>-1.0488</v>
       </c>
       <c r="N71" t="n">
-        <v>172</v>
+        <v>153</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ztr</t>
+          <t>reck</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-1.0578</v>
+        <v>-1.2175</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.4204</v>
+        <v>-0.4838</v>
       </c>
       <c r="D72" t="n">
-        <v>-1.1057</v>
+        <v>-1.1577</v>
       </c>
       <c r="E72" t="n">
-        <v>-1.0578</v>
+        <v>-1.2175</v>
       </c>
       <c r="F72" t="n">
-        <v>-1.0578</v>
+        <v>-0.9224</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>-1.0578</v>
+        <v>-0.9224</v>
       </c>
       <c r="I72" t="n">
-        <v>-1.0578</v>
+        <v>-0.9224</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>153</v>
+        <v>172</v>
       </c>
       <c r="L72" t="n">
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>-1.0578</v>
+        <v>-0.9224</v>
       </c>
       <c r="N72" t="n">
-        <v>153</v>
+        <v>172</v>
       </c>
     </row>
     <row r="73">
@@ -3762,16 +3762,16 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-1.2927</v>
+        <v>-1.3556</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.5137</v>
+        <v>-0.5387</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.2127</v>
+        <v>-1.2193</v>
       </c>
       <c r="E73" t="n">
-        <v>-1.2927</v>
+        <v>-1.3556</v>
       </c>
       <c r="F73" t="n">
         <v>-1.2927</v>
@@ -3808,28 +3808,28 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-1.6284</v>
+        <v>-1.8666</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.6471</v>
+        <v>-0.7418</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.3655</v>
+        <v>-1.4476</v>
       </c>
       <c r="E74" t="n">
-        <v>-1.6284</v>
+        <v>-1.8666</v>
       </c>
       <c r="F74" t="n">
-        <v>-1.6284</v>
+        <v>-1.6382</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>-1.6284</v>
+        <v>-1.6382</v>
       </c>
       <c r="I74" t="n">
-        <v>-1.6284</v>
+        <v>-1.6382</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -3841,7 +3841,7 @@
         <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>-1.6284</v>
+        <v>-1.6382</v>
       </c>
       <c r="N74" t="n">
         <v>276</v>
@@ -3854,28 +3854,28 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-1.687</v>
+        <v>-2.1793</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.6704</v>
+        <v>-0.8661</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.3922</v>
+        <v>-1.5873</v>
       </c>
       <c r="E75" t="n">
-        <v>-1.687</v>
+        <v>-2.1793</v>
       </c>
       <c r="F75" t="n">
-        <v>-1.687</v>
+        <v>-1.7137</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>-1.687</v>
+        <v>-1.7137</v>
       </c>
       <c r="I75" t="n">
-        <v>-1.687</v>
+        <v>-1.7137</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -3887,7 +3887,7 @@
         <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>-1.687</v>
+        <v>-1.7137</v>
       </c>
       <c r="N75" t="n">
         <v>77</v>
@@ -3896,47 +3896,47 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>sl3nd</t>
+          <t>Lucaozy</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-2.1436</v>
+        <v>-2.5116</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.8519</v>
+        <v>-0.9981</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.6</v>
+        <v>-1.7357</v>
       </c>
       <c r="E76" t="n">
-        <v>-2.1436</v>
+        <v>-2.5116</v>
       </c>
       <c r="F76" t="n">
-        <v>-2.1436</v>
+        <v>-2.3551</v>
       </c>
       <c r="G76" t="n">
-        <v>0</v>
+        <v>-0.1123</v>
       </c>
       <c r="H76" t="n">
-        <v>-2.1436</v>
+        <v>-2.3551</v>
       </c>
       <c r="I76" t="n">
-        <v>-2.1436</v>
+        <v>-2.4158</v>
       </c>
       <c r="J76" t="n">
-        <v>0</v>
+        <v>-0.1123</v>
       </c>
       <c r="K76" t="n">
-        <v>153</v>
+        <v>271</v>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="M76" t="n">
-        <v>-2.1436</v>
+        <v>-2.5281</v>
       </c>
       <c r="N76" t="n">
-        <v>153</v>
+        <v>315</v>
       </c>
     </row>
     <row r="77">
@@ -3946,31 +3946,31 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-2.3461</v>
+        <v>-2.532</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.9324</v>
+        <v>-1.0062</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.6922</v>
+        <v>-1.7448</v>
       </c>
       <c r="E77" t="n">
-        <v>-2.3461</v>
+        <v>-2.532</v>
       </c>
       <c r="F77" t="n">
-        <v>-1.392</v>
+        <v>-1.3921</v>
       </c>
       <c r="G77" t="n">
-        <v>-0.9540999999999999</v>
+        <v>-0.9505</v>
       </c>
       <c r="H77" t="n">
-        <v>-1.392</v>
+        <v>-1.3921</v>
       </c>
       <c r="I77" t="n">
-        <v>-1.4279</v>
+        <v>-1.428</v>
       </c>
       <c r="J77" t="n">
-        <v>-0.9540999999999999</v>
+        <v>-0.9505</v>
       </c>
       <c r="K77" t="n">
         <v>356</v>
@@ -3979,7 +3979,7 @@
         <v>109</v>
       </c>
       <c r="M77" t="n">
-        <v>-2.382</v>
+        <v>-2.3785</v>
       </c>
       <c r="N77" t="n">
         <v>465</v>
@@ -3992,28 +3992,28 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-2.3585</v>
+        <v>-2.6002</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.9373</v>
+        <v>-1.0333</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.6978</v>
+        <v>-1.7753</v>
       </c>
       <c r="E78" t="n">
-        <v>-2.3585</v>
+        <v>-2.6002</v>
       </c>
       <c r="F78" t="n">
-        <v>-2.3585</v>
+        <v>-2.3586</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>-2.3585</v>
+        <v>-2.3586</v>
       </c>
       <c r="I78" t="n">
-        <v>-2.3585</v>
+        <v>-2.3586</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -4025,7 +4025,7 @@
         <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>-2.3585</v>
+        <v>-2.3586</v>
       </c>
       <c r="N78" t="n">
         <v>240</v>
@@ -4034,139 +4034,139 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Lucaozy</t>
+          <t>sl3nd</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-2.4434</v>
+        <v>-2.6055</v>
       </c>
       <c r="C79" t="n">
-        <v>-0.971</v>
+        <v>-1.0354</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.7365</v>
+        <v>-1.7776</v>
       </c>
       <c r="E79" t="n">
-        <v>-2.4434</v>
+        <v>-2.6055</v>
       </c>
       <c r="F79" t="n">
-        <v>-2.3311</v>
+        <v>-2.1437</v>
       </c>
       <c r="G79" t="n">
-        <v>-0.1123</v>
+        <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>-2.3311</v>
+        <v>-2.1437</v>
       </c>
       <c r="I79" t="n">
-        <v>-2.3912</v>
+        <v>-2.1437</v>
       </c>
       <c r="J79" t="n">
-        <v>-0.1123</v>
+        <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>271</v>
+        <v>153</v>
       </c>
       <c r="L79" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>-2.5035</v>
+        <v>-2.1437</v>
       </c>
       <c r="N79" t="n">
-        <v>315</v>
+        <v>153</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>chopper</t>
+          <t>WOOD7</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-2.8924</v>
+        <v>-3.0931</v>
       </c>
       <c r="C80" t="n">
-        <v>-1.1495</v>
+        <v>-1.2292</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.9409</v>
+        <v>-1.9954</v>
       </c>
       <c r="E80" t="n">
-        <v>-2.8924</v>
+        <v>-3.0931</v>
       </c>
       <c r="F80" t="n">
-        <v>-3.8103</v>
+        <v>-2.9653</v>
       </c>
       <c r="G80" t="n">
-        <v>0.9179</v>
+        <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>-3.8103</v>
+        <v>-2.9653</v>
       </c>
       <c r="I80" t="n">
-        <v>-3.8103</v>
+        <v>-2.9653</v>
       </c>
       <c r="J80" t="n">
-        <v>0.9179</v>
+        <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>132</v>
+        <v>240</v>
       </c>
       <c r="L80" t="n">
-        <v>195</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>-2.8924</v>
+        <v>-2.9653</v>
       </c>
       <c r="N80" t="n">
-        <v>327</v>
+        <v>240</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>WOOD7</t>
+          <t>chopper</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-2.9651</v>
+        <v>-3.1583</v>
       </c>
       <c r="C81" t="n">
-        <v>-1.1783</v>
+        <v>-1.2551</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.974</v>
+        <v>-2.0246</v>
       </c>
       <c r="E81" t="n">
-        <v>-2.9651</v>
+        <v>-3.1583</v>
       </c>
       <c r="F81" t="n">
-        <v>-2.9651</v>
+        <v>-3.8103</v>
       </c>
       <c r="G81" t="n">
-        <v>0</v>
+        <v>0.9179</v>
       </c>
       <c r="H81" t="n">
-        <v>-2.9651</v>
+        <v>-3.8103</v>
       </c>
       <c r="I81" t="n">
-        <v>-2.9651</v>
+        <v>-3.8103</v>
       </c>
       <c r="J81" t="n">
-        <v>0</v>
+        <v>0.9179</v>
       </c>
       <c r="K81" t="n">
-        <v>240</v>
+        <v>132</v>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>195</v>
       </c>
       <c r="M81" t="n">
-        <v>-2.9651</v>
+        <v>-2.8924</v>
       </c>
       <c r="N81" t="n">
-        <v>240</v>
+        <v>327</v>
       </c>
     </row>
     <row r="82">
@@ -4176,31 +4176,31 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>-3.8367</v>
+        <v>-4.0763</v>
       </c>
       <c r="C82" t="n">
-        <v>-1.5247</v>
+        <v>-1.6199</v>
       </c>
       <c r="D82" t="n">
-        <v>-2.3707</v>
+        <v>-2.4346</v>
       </c>
       <c r="E82" t="n">
-        <v>-3.8367</v>
+        <v>-4.0763</v>
       </c>
       <c r="F82" t="n">
-        <v>-3.2842</v>
+        <v>-3.2847</v>
       </c>
       <c r="G82" t="n">
-        <v>-0.5525</v>
+        <v>-0.5527</v>
       </c>
       <c r="H82" t="n">
-        <v>-3.2842</v>
+        <v>-3.2847</v>
       </c>
       <c r="I82" t="n">
-        <v>-3.3688</v>
+        <v>-3.3693</v>
       </c>
       <c r="J82" t="n">
-        <v>-0.5525</v>
+        <v>-0.5527</v>
       </c>
       <c r="K82" t="n">
         <v>266</v>
@@ -4209,7 +4209,7 @@
         <v>45</v>
       </c>
       <c r="M82" t="n">
-        <v>-3.9213</v>
+        <v>-3.922</v>
       </c>
       <c r="N82" t="n">
         <v>311</v>
@@ -8315,10 +8315,10 @@
         <v>1.52</v>
       </c>
       <c r="I102" t="n">
-        <v>0.6088</v>
+        <v>0.6091</v>
       </c>
       <c r="J102" t="n">
-        <v>14.6112</v>
+        <v>14.6184</v>
       </c>
     </row>
     <row r="103">
@@ -8355,10 +8355,10 @@
         <v>1.34</v>
       </c>
       <c r="I103" t="n">
-        <v>0.4649</v>
+        <v>0.4652</v>
       </c>
       <c r="J103" t="n">
-        <v>11.1576</v>
+        <v>11.1648</v>
       </c>
     </row>
     <row r="104">
@@ -8395,10 +8395,10 @@
         <v>1.18</v>
       </c>
       <c r="I104" t="n">
-        <v>0.2852</v>
+        <v>0.2855</v>
       </c>
       <c r="J104" t="n">
-        <v>6.8448</v>
+        <v>6.852</v>
       </c>
     </row>
     <row r="105">
@@ -8432,13 +8432,13 @@
         <v>24</v>
       </c>
       <c r="H105" t="n">
-        <v>0.82</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.2394</v>
+        <v>-0.2493</v>
       </c>
       <c r="J105" t="n">
-        <v>-5.7456</v>
+        <v>-5.9832</v>
       </c>
     </row>
     <row r="106">
@@ -8475,10 +8475,10 @@
         <v>0.54</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.4947</v>
+        <v>-0.4946</v>
       </c>
       <c r="J106" t="n">
-        <v>-11.8728</v>
+        <v>-11.8704</v>
       </c>
     </row>
     <row r="107">
@@ -8715,10 +8715,10 @@
         <v>1.02</v>
       </c>
       <c r="I112" t="n">
-        <v>0.0941</v>
+        <v>0.0936</v>
       </c>
       <c r="J112" t="n">
-        <v>1.9761</v>
+        <v>1.9656</v>
       </c>
     </row>
     <row r="113">
@@ -8755,10 +8755,10 @@
         <v>1.01</v>
       </c>
       <c r="I113" t="n">
-        <v>0.063</v>
+        <v>0.0625</v>
       </c>
       <c r="J113" t="n">
-        <v>1.323</v>
+        <v>1.3125</v>
       </c>
     </row>
     <row r="114">
@@ -8792,13 +8792,13 @@
         <v>21</v>
       </c>
       <c r="H114" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.0776</v>
+        <v>-0.0641</v>
       </c>
       <c r="J114" t="n">
-        <v>-1.6296</v>
+        <v>-1.3461</v>
       </c>
     </row>
     <row r="115">
@@ -8835,10 +8835,10 @@
         <v>0.76</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.2802</v>
+        <v>-0.2804</v>
       </c>
       <c r="J115" t="n">
-        <v>-5.8842</v>
+        <v>-5.8884</v>
       </c>
     </row>
     <row r="116">
@@ -8875,10 +8875,10 @@
         <v>0.68</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.3549</v>
+        <v>-0.3552</v>
       </c>
       <c r="J116" t="n">
-        <v>-7.4529</v>
+        <v>-7.4592</v>
       </c>
     </row>
     <row r="117">
@@ -9315,10 +9315,10 @@
         <v>2.13</v>
       </c>
       <c r="I127" t="n">
-        <v>1.6693</v>
+        <v>1.6689</v>
       </c>
       <c r="J127" t="n">
-        <v>26.7088</v>
+        <v>26.7024</v>
       </c>
     </row>
     <row r="128">
@@ -9352,13 +9352,13 @@
         <v>16</v>
       </c>
       <c r="H128" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="I128" t="n">
-        <v>1.4269</v>
+        <v>1.4383</v>
       </c>
       <c r="J128" t="n">
-        <v>22.8304</v>
+        <v>23.0128</v>
       </c>
     </row>
     <row r="129">
@@ -9395,10 +9395,10 @@
         <v>1.47</v>
       </c>
       <c r="I129" t="n">
-        <v>0.8773</v>
+        <v>0.8771</v>
       </c>
       <c r="J129" t="n">
-        <v>14.0368</v>
+        <v>14.0336</v>
       </c>
     </row>
     <row r="130">
@@ -9435,10 +9435,10 @@
         <v>1.01</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.0209</v>
+        <v>-0.0212</v>
       </c>
       <c r="J130" t="n">
-        <v>-0.3344</v>
+        <v>-0.3392</v>
       </c>
     </row>
     <row r="131">
@@ -9475,10 +9475,10 @@
         <v>0.99</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.1404</v>
+        <v>-0.1407</v>
       </c>
       <c r="J131" t="n">
-        <v>-2.2464</v>
+        <v>-2.2512</v>
       </c>
     </row>
     <row r="132">
@@ -10115,10 +10115,10 @@
         <v>1.2</v>
       </c>
       <c r="I147" t="n">
-        <v>0.4474</v>
+        <v>0.4469</v>
       </c>
       <c r="J147" t="n">
-        <v>10.7376</v>
+        <v>10.7256</v>
       </c>
     </row>
     <row r="148">
@@ -10152,13 +10152,13 @@
         <v>24</v>
       </c>
       <c r="H148" t="n">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.1067</v>
+        <v>-0.09470000000000001</v>
       </c>
       <c r="J148" t="n">
-        <v>-2.5608</v>
+        <v>-2.2728</v>
       </c>
     </row>
     <row r="149">
@@ -10195,10 +10195,10 @@
         <v>0.89</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.1523</v>
+        <v>-0.1525</v>
       </c>
       <c r="J149" t="n">
-        <v>-3.6552</v>
+        <v>-3.66</v>
       </c>
     </row>
     <row r="150">
@@ -10235,10 +10235,10 @@
         <v>0.86</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.1846</v>
+        <v>-0.1848</v>
       </c>
       <c r="J150" t="n">
-        <v>-4.4304</v>
+        <v>-4.4352</v>
       </c>
     </row>
     <row r="151">
@@ -10275,10 +10275,10 @@
         <v>0.77</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.2752</v>
+        <v>-0.2754</v>
       </c>
       <c r="J151" t="n">
-        <v>-6.6048</v>
+        <v>-6.6096</v>
       </c>
     </row>
     <row r="152">
@@ -11712,13 +11712,13 @@
         <v>21</v>
       </c>
       <c r="H187" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="I187" t="n">
-        <v>0.7766999999999999</v>
+        <v>0.7844</v>
       </c>
       <c r="J187" t="n">
-        <v>16.3107</v>
+        <v>16.4724</v>
       </c>
     </row>
     <row r="188">
@@ -11755,10 +11755,10 @@
         <v>1.02</v>
       </c>
       <c r="I188" t="n">
-        <v>0.07439999999999999</v>
+        <v>0.0741</v>
       </c>
       <c r="J188" t="n">
-        <v>1.5624</v>
+        <v>1.5561</v>
       </c>
     </row>
     <row r="189">
@@ -11795,10 +11795,10 @@
         <v>0.77</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.2702</v>
+        <v>-0.2704</v>
       </c>
       <c r="J189" t="n">
-        <v>-5.6742</v>
+        <v>-5.6784</v>
       </c>
     </row>
     <row r="190">
@@ -11835,10 +11835,10 @@
         <v>0.64</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.3908</v>
+        <v>-0.391</v>
       </c>
       <c r="J190" t="n">
-        <v>-8.206799999999999</v>
+        <v>-8.211</v>
       </c>
     </row>
     <row r="191">
@@ -11875,10 +11875,10 @@
         <v>0.34</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.6475</v>
+        <v>-0.6476</v>
       </c>
       <c r="J191" t="n">
-        <v>-13.5975</v>
+        <v>-13.5996</v>
       </c>
     </row>
     <row r="192">
@@ -13115,10 +13115,10 @@
         <v>1.42</v>
       </c>
       <c r="I222" t="n">
-        <v>1.0038</v>
+        <v>1.0044</v>
       </c>
       <c r="J222" t="n">
-        <v>24.0912</v>
+        <v>24.1056</v>
       </c>
     </row>
     <row r="223">
@@ -13155,16 +13155,16 @@
         <v>1.12</v>
       </c>
       <c r="I223" t="n">
-        <v>0.3717</v>
+        <v>0.3718</v>
       </c>
       <c r="J223" t="n">
-        <v>8.9208</v>
+        <v>8.9232</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Lucaozy</t>
+          <t>saffee</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -13195,16 +13195,16 @@
         <v>1.12</v>
       </c>
       <c r="I224" t="n">
-        <v>0.3717</v>
+        <v>0.3718</v>
       </c>
       <c r="J224" t="n">
-        <v>8.9208</v>
+        <v>8.9232</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>saffee</t>
+          <t>Lucaozy</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -13232,13 +13232,13 @@
         <v>24</v>
       </c>
       <c r="H225" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="I225" t="n">
-        <v>0.3717</v>
+        <v>0.3475</v>
       </c>
       <c r="J225" t="n">
-        <v>8.9208</v>
+        <v>8.34</v>
       </c>
     </row>
     <row r="226">
@@ -13275,10 +13275,10 @@
         <v>0.83</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.5414</v>
+        <v>-0.5411</v>
       </c>
       <c r="J226" t="n">
-        <v>-12.9936</v>
+        <v>-12.9864</v>
       </c>
     </row>
     <row r="227">
@@ -15515,10 +15515,10 @@
         <v>1.32</v>
       </c>
       <c r="I282" t="n">
-        <v>0.8116</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="J282" t="n">
-        <v>18.6668</v>
+        <v>18.653</v>
       </c>
     </row>
     <row r="283">
@@ -15552,13 +15552,13 @@
         <v>23</v>
       </c>
       <c r="H283" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="I283" t="n">
-        <v>0.7288</v>
+        <v>0.7492</v>
       </c>
       <c r="J283" t="n">
-        <v>16.7624</v>
+        <v>17.2316</v>
       </c>
     </row>
     <row r="284">
@@ -15595,10 +15595,10 @@
         <v>1.19</v>
       </c>
       <c r="I284" t="n">
-        <v>0.5341</v>
+        <v>0.5337</v>
       </c>
       <c r="J284" t="n">
-        <v>12.2843</v>
+        <v>12.2751</v>
       </c>
     </row>
     <row r="285">
@@ -15635,10 +15635,10 @@
         <v>1.1</v>
       </c>
       <c r="I285" t="n">
-        <v>0.322</v>
+        <v>0.3217</v>
       </c>
       <c r="J285" t="n">
-        <v>7.406</v>
+        <v>7.3991</v>
       </c>
     </row>
     <row r="286">
@@ -15675,10 +15675,10 @@
         <v>0.72</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.7894</v>
+        <v>-0.7897</v>
       </c>
       <c r="J286" t="n">
-        <v>-18.1562</v>
+        <v>-18.1631</v>
       </c>
     </row>
     <row r="287">
@@ -15715,10 +15715,10 @@
         <v>1.11</v>
       </c>
       <c r="I287" t="n">
-        <v>0.2823</v>
+        <v>0.2827</v>
       </c>
       <c r="J287" t="n">
-        <v>6.4929</v>
+        <v>6.5021</v>
       </c>
     </row>
     <row r="288">
@@ -15755,10 +15755,10 @@
         <v>1.07</v>
       </c>
       <c r="I288" t="n">
-        <v>0.2008</v>
+        <v>0.2012</v>
       </c>
       <c r="J288" t="n">
-        <v>4.6184</v>
+        <v>4.6276</v>
       </c>
     </row>
     <row r="289">
@@ -15795,10 +15795,10 @@
         <v>0.92</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.1197</v>
+        <v>-0.1195</v>
       </c>
       <c r="J289" t="n">
-        <v>-2.7531</v>
+        <v>-2.7485</v>
       </c>
     </row>
     <row r="290">
@@ -15832,13 +15832,13 @@
         <v>23</v>
       </c>
       <c r="H290" t="n">
-        <v>0.83</v>
+        <v>0.82</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.2176</v>
+        <v>-0.2276</v>
       </c>
       <c r="J290" t="n">
-        <v>-5.0048</v>
+        <v>-5.2348</v>
       </c>
     </row>
     <row r="291">
@@ -15875,10 +15875,10 @@
         <v>0.82</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.2278</v>
+        <v>-0.2276</v>
       </c>
       <c r="J291" t="n">
-        <v>-5.2394</v>
+        <v>-5.2348</v>
       </c>
     </row>
     <row r="292">
@@ -16712,13 +16712,13 @@
         <v>20</v>
       </c>
       <c r="H312" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="I312" t="n">
-        <v>1.7405</v>
+        <v>1.729</v>
       </c>
       <c r="J312" t="n">
-        <v>34.81</v>
+        <v>34.58</v>
       </c>
     </row>
     <row r="313">
@@ -16755,10 +16755,10 @@
         <v>1.23</v>
       </c>
       <c r="I313" t="n">
-        <v>0.6021</v>
+        <v>0.6022999999999999</v>
       </c>
       <c r="J313" t="n">
-        <v>12.042</v>
+        <v>12.046</v>
       </c>
     </row>
     <row r="314">
@@ -16795,10 +16795,10 @@
         <v>1.17</v>
       </c>
       <c r="I314" t="n">
-        <v>0.4705</v>
+        <v>0.4708</v>
       </c>
       <c r="J314" t="n">
-        <v>9.41</v>
+        <v>9.416</v>
       </c>
     </row>
     <row r="315">
@@ -16835,10 +16835,10 @@
         <v>1.14</v>
       </c>
       <c r="I315" t="n">
-        <v>0.4001</v>
+        <v>0.4004</v>
       </c>
       <c r="J315" t="n">
-        <v>8.002000000000001</v>
+        <v>8.007999999999999</v>
       </c>
     </row>
     <row r="316">
@@ -16875,10 +16875,10 @@
         <v>0.77</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.7033</v>
+        <v>-0.703</v>
       </c>
       <c r="J316" t="n">
-        <v>-14.066</v>
+        <v>-14.06</v>
       </c>
     </row>
     <row r="317">
@@ -17084,7 +17084,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Lucaozy</t>
+          <t>insani</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -17124,7 +17124,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>insani</t>
+          <t>Lucaozy</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -17312,13 +17312,13 @@
         <v>21</v>
       </c>
       <c r="H327" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="I327" t="n">
-        <v>0.2891</v>
+        <v>0.308</v>
       </c>
       <c r="J327" t="n">
-        <v>6.0711</v>
+        <v>6.468</v>
       </c>
     </row>
     <row r="328">
@@ -17355,10 +17355,10 @@
         <v>1.08</v>
       </c>
       <c r="I328" t="n">
-        <v>0.2282</v>
+        <v>0.2277</v>
       </c>
       <c r="J328" t="n">
-        <v>4.7922</v>
+        <v>4.7817</v>
       </c>
     </row>
     <row r="329">
@@ -17395,10 +17395,10 @@
         <v>1.07</v>
       </c>
       <c r="I329" t="n">
-        <v>0.2069</v>
+        <v>0.2064</v>
       </c>
       <c r="J329" t="n">
-        <v>4.3449</v>
+        <v>4.3344</v>
       </c>
     </row>
     <row r="330">
@@ -17435,10 +17435,10 @@
         <v>0.84</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.2048</v>
+        <v>-0.2049</v>
       </c>
       <c r="J330" t="n">
-        <v>-4.3008</v>
+        <v>-4.3029</v>
       </c>
     </row>
     <row r="331">
@@ -17475,10 +17475,10 @@
         <v>0.51</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.5084</v>
+        <v>-0.5086000000000001</v>
       </c>
       <c r="J331" t="n">
-        <v>-10.6764</v>
+        <v>-10.6806</v>
       </c>
     </row>
     <row r="332">
@@ -17712,13 +17712,13 @@
         <v>36</v>
       </c>
       <c r="H337" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="I337" t="n">
-        <v>0.9429</v>
+        <v>0.9557</v>
       </c>
       <c r="J337" t="n">
-        <v>33.9444</v>
+        <v>34.4052</v>
       </c>
     </row>
     <row r="338">
@@ -17755,10 +17755,10 @@
         <v>0.98</v>
       </c>
       <c r="I338" t="n">
-        <v>-0.0423</v>
+        <v>-0.0425</v>
       </c>
       <c r="J338" t="n">
-        <v>-1.5228</v>
+        <v>-1.53</v>
       </c>
     </row>
     <row r="339">
@@ -17795,10 +17795,10 @@
         <v>0.86</v>
       </c>
       <c r="I339" t="n">
-        <v>-0.1904</v>
+        <v>-0.1906</v>
       </c>
       <c r="J339" t="n">
-        <v>-6.8544</v>
+        <v>-6.8616</v>
       </c>
     </row>
     <row r="340">
@@ -17835,10 +17835,10 @@
         <v>0.84</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.2114</v>
+        <v>-0.2115</v>
       </c>
       <c r="J340" t="n">
-        <v>-7.6104</v>
+        <v>-7.614</v>
       </c>
     </row>
     <row r="341">
@@ -17875,10 +17875,10 @@
         <v>0.76</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.2909</v>
+        <v>-0.291</v>
       </c>
       <c r="J341" t="n">
-        <v>-10.4724</v>
+        <v>-10.476</v>
       </c>
     </row>
     <row r="342">
@@ -19715,10 +19715,10 @@
         <v>1.29</v>
       </c>
       <c r="I387" t="n">
-        <v>0.5716</v>
+        <v>0.5711000000000001</v>
       </c>
       <c r="J387" t="n">
-        <v>13.1468</v>
+        <v>13.1353</v>
       </c>
     </row>
     <row r="388">
@@ -19755,10 +19755,10 @@
         <v>1.21</v>
       </c>
       <c r="I388" t="n">
-        <v>0.4422</v>
+        <v>0.4417</v>
       </c>
       <c r="J388" t="n">
-        <v>10.1706</v>
+        <v>10.1591</v>
       </c>
     </row>
     <row r="389">
@@ -19795,10 +19795,10 @@
         <v>1.02</v>
       </c>
       <c r="I389" t="n">
-        <v>0.0702</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J389" t="n">
-        <v>1.6146</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="390">
@@ -19835,10 +19835,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I390" t="n">
-        <v>-0.1021</v>
+        <v>-0.1022</v>
       </c>
       <c r="J390" t="n">
-        <v>-2.3483</v>
+        <v>-2.3506</v>
       </c>
     </row>
     <row r="391">
@@ -19872,13 +19872,13 @@
         <v>23</v>
       </c>
       <c r="H391" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="I391" t="n">
-        <v>-0.3232</v>
+        <v>-0.3139</v>
       </c>
       <c r="J391" t="n">
-        <v>-7.4336</v>
+        <v>-7.2197</v>
       </c>
     </row>
     <row r="392">
@@ -20315,10 +20315,10 @@
         <v>2.13</v>
       </c>
       <c r="I402" t="n">
-        <v>1.921</v>
+        <v>1.9202</v>
       </c>
       <c r="J402" t="n">
-        <v>38.42</v>
+        <v>38.404</v>
       </c>
     </row>
     <row r="403">
@@ -20355,10 +20355,10 @@
         <v>1.24</v>
       </c>
       <c r="I403" t="n">
-        <v>0.634</v>
+        <v>0.6337</v>
       </c>
       <c r="J403" t="n">
-        <v>12.68</v>
+        <v>12.674</v>
       </c>
     </row>
     <row r="404">
@@ -20392,13 +20392,13 @@
         <v>20</v>
       </c>
       <c r="H404" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="I404" t="n">
-        <v>0.3899</v>
+        <v>0.4136</v>
       </c>
       <c r="J404" t="n">
-        <v>7.798</v>
+        <v>8.272</v>
       </c>
     </row>
     <row r="405">
@@ -20435,10 +20435,10 @@
         <v>0.73</v>
       </c>
       <c r="I405" t="n">
-        <v>-0.7763</v>
+        <v>-0.7766999999999999</v>
       </c>
       <c r="J405" t="n">
-        <v>-15.526</v>
+        <v>-15.534</v>
       </c>
     </row>
     <row r="406">
@@ -20475,10 +20475,10 @@
         <v>0.63</v>
       </c>
       <c r="I406" t="n">
-        <v>-0.9856</v>
+        <v>-0.9859</v>
       </c>
       <c r="J406" t="n">
-        <v>-19.712</v>
+        <v>-19.718</v>
       </c>
     </row>
     <row r="407">
@@ -23515,10 +23515,10 @@
         <v>1.2</v>
       </c>
       <c r="I482" t="n">
-        <v>0.5664</v>
+        <v>0.5659</v>
       </c>
       <c r="J482" t="n">
-        <v>13.5936</v>
+        <v>13.5816</v>
       </c>
     </row>
     <row r="483">
@@ -23555,10 +23555,10 @@
         <v>1.16</v>
       </c>
       <c r="I483" t="n">
-        <v>0.4742</v>
+        <v>0.4738</v>
       </c>
       <c r="J483" t="n">
-        <v>11.3808</v>
+        <v>11.3712</v>
       </c>
     </row>
     <row r="484">
@@ -23592,13 +23592,13 @@
         <v>24</v>
       </c>
       <c r="H484" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="I484" t="n">
-        <v>0.3525</v>
+        <v>0.3772</v>
       </c>
       <c r="J484" t="n">
-        <v>8.460000000000001</v>
+        <v>9.0528</v>
       </c>
     </row>
     <row r="485">
@@ -23635,10 +23635,10 @@
         <v>0.96</v>
       </c>
       <c r="I485" t="n">
-        <v>-0.1826</v>
+        <v>-0.183</v>
       </c>
       <c r="J485" t="n">
-        <v>-4.3824</v>
+        <v>-4.392</v>
       </c>
     </row>
     <row r="486">
@@ -23675,10 +23675,10 @@
         <v>0.95</v>
       </c>
       <c r="I486" t="n">
-        <v>-0.2144</v>
+        <v>-0.2148</v>
       </c>
       <c r="J486" t="n">
-        <v>-5.1456</v>
+        <v>-5.1552</v>
       </c>
     </row>
     <row r="487">
@@ -23884,7 +23884,7 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>sjuush</t>
+          <t>ewjerkz</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
@@ -23912,19 +23912,19 @@
         <v>23</v>
       </c>
       <c r="H492" t="n">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="I492" t="n">
-        <v>-0.0325</v>
+        <v>-0.0148</v>
       </c>
       <c r="J492" t="n">
-        <v>-0.7475000000000001</v>
+        <v>-0.3404</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>ewjerkz</t>
+          <t>sjuush</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
@@ -23955,10 +23955,10 @@
         <v>0.98</v>
       </c>
       <c r="I493" t="n">
-        <v>-0.0325</v>
+        <v>-0.0328</v>
       </c>
       <c r="J493" t="n">
-        <v>-0.7475000000000001</v>
+        <v>-0.7544</v>
       </c>
     </row>
     <row r="494">
@@ -23995,10 +23995,10 @@
         <v>0.86</v>
       </c>
       <c r="I494" t="n">
-        <v>-0.1804</v>
+        <v>-0.1805</v>
       </c>
       <c r="J494" t="n">
-        <v>-4.1492</v>
+        <v>-4.1515</v>
       </c>
     </row>
     <row r="495">
@@ -24035,10 +24035,10 @@
         <v>0.85</v>
       </c>
       <c r="I495" t="n">
-        <v>-0.1907</v>
+        <v>-0.1908</v>
       </c>
       <c r="J495" t="n">
-        <v>-4.3861</v>
+        <v>-4.3884</v>
       </c>
     </row>
     <row r="496">
@@ -24075,10 +24075,10 @@
         <v>0.72</v>
       </c>
       <c r="I496" t="n">
-        <v>-0.3174</v>
+        <v>-0.3176</v>
       </c>
       <c r="J496" t="n">
-        <v>-7.3002</v>
+        <v>-7.3048</v>
       </c>
     </row>
     <row r="497">
@@ -25515,10 +25515,10 @@
         <v>1.29</v>
       </c>
       <c r="I532" t="n">
-        <v>0.6448</v>
+        <v>0.6429</v>
       </c>
       <c r="J532" t="n">
-        <v>12.2512</v>
+        <v>12.2151</v>
       </c>
     </row>
     <row r="533">
@@ -25552,13 +25552,13 @@
         <v>19</v>
       </c>
       <c r="H533" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="I533" t="n">
-        <v>0.338</v>
+        <v>0.3756</v>
       </c>
       <c r="J533" t="n">
-        <v>6.422</v>
+        <v>7.1364</v>
       </c>
     </row>
     <row r="534">
@@ -25595,10 +25595,10 @@
         <v>0.64</v>
       </c>
       <c r="I534" t="n">
-        <v>-0.3853</v>
+        <v>-0.3857</v>
       </c>
       <c r="J534" t="n">
-        <v>-7.3207</v>
+        <v>-7.3283</v>
       </c>
     </row>
     <row r="535">
@@ -25635,10 +25635,10 @@
         <v>0.6</v>
       </c>
       <c r="I535" t="n">
-        <v>-0.421</v>
+        <v>-0.4214</v>
       </c>
       <c r="J535" t="n">
-        <v>-7.999</v>
+        <v>-8.006600000000001</v>
       </c>
     </row>
     <row r="536">
@@ -25675,10 +25675,10 @@
         <v>0.49</v>
       </c>
       <c r="I536" t="n">
-        <v>-0.517</v>
+        <v>-0.5174</v>
       </c>
       <c r="J536" t="n">
-        <v>-9.823</v>
+        <v>-9.8306</v>
       </c>
     </row>
     <row r="537">
@@ -27315,10 +27315,10 @@
         <v>1.52</v>
       </c>
       <c r="I577" t="n">
-        <v>0.655</v>
+        <v>0.6546999999999999</v>
       </c>
       <c r="J577" t="n">
-        <v>15.72</v>
+        <v>15.7128</v>
       </c>
     </row>
     <row r="578">
@@ -27352,13 +27352,13 @@
         <v>24</v>
       </c>
       <c r="H578" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="I578" t="n">
-        <v>0.54</v>
+        <v>0.5503</v>
       </c>
       <c r="J578" t="n">
-        <v>12.96</v>
+        <v>13.2072</v>
       </c>
     </row>
     <row r="579">
@@ -27395,10 +27395,10 @@
         <v>1.1</v>
       </c>
       <c r="I579" t="n">
-        <v>0.1748</v>
+        <v>0.1747</v>
       </c>
       <c r="J579" t="n">
-        <v>4.1952</v>
+        <v>4.1928</v>
       </c>
     </row>
     <row r="580">
@@ -27435,10 +27435,10 @@
         <v>0.98</v>
       </c>
       <c r="I580" t="n">
-        <v>-0.0538</v>
+        <v>-0.0539</v>
       </c>
       <c r="J580" t="n">
-        <v>-1.2912</v>
+        <v>-1.2936</v>
       </c>
     </row>
     <row r="581">
@@ -27475,10 +27475,10 @@
         <v>0.72</v>
       </c>
       <c r="I581" t="n">
-        <v>-0.341</v>
+        <v>-0.3411</v>
       </c>
       <c r="J581" t="n">
-        <v>-8.183999999999999</v>
+        <v>-8.186400000000001</v>
       </c>
     </row>
     <row r="582">
@@ -27715,16 +27715,16 @@
         <v>1.1</v>
       </c>
       <c r="I587" t="n">
-        <v>0.3034</v>
+        <v>0.3019</v>
       </c>
       <c r="J587" t="n">
-        <v>6.3714</v>
+        <v>6.3399</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>Lucaozy</t>
+          <t>saffee</t>
         </is>
       </c>
       <c r="B588" t="inlineStr">
@@ -27752,19 +27752,19 @@
         <v>21</v>
       </c>
       <c r="H588" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="I588" t="n">
-        <v>-0.054</v>
+        <v>-0.0397</v>
       </c>
       <c r="J588" t="n">
-        <v>-1.134</v>
+        <v>-0.8337</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>saffee</t>
+          <t>Lucaozy</t>
         </is>
       </c>
       <c r="B589" t="inlineStr">
@@ -27795,10 +27795,10 @@
         <v>0.96</v>
       </c>
       <c r="I589" t="n">
-        <v>-0.054</v>
+        <v>-0.0546</v>
       </c>
       <c r="J589" t="n">
-        <v>-1.134</v>
+        <v>-1.1466</v>
       </c>
     </row>
     <row r="590">
@@ -27832,13 +27832,13 @@
         <v>21</v>
       </c>
       <c r="H590" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="I590" t="n">
-        <v>-0.4014</v>
+        <v>-0.3929</v>
       </c>
       <c r="J590" t="n">
-        <v>-8.429399999999999</v>
+        <v>-8.2509</v>
       </c>
     </row>
     <row r="591">
@@ -27875,10 +27875,10 @@
         <v>0.42</v>
       </c>
       <c r="I591" t="n">
-        <v>-0.5753</v>
+        <v>-0.5756</v>
       </c>
       <c r="J591" t="n">
-        <v>-12.0813</v>
+        <v>-12.0876</v>
       </c>
     </row>
     <row r="592">
@@ -29115,10 +29115,10 @@
         <v>1.89</v>
       </c>
       <c r="I622" t="n">
-        <v>0.9509</v>
+        <v>0.9510999999999999</v>
       </c>
       <c r="J622" t="n">
-        <v>15.2144</v>
+        <v>15.2176</v>
       </c>
     </row>
     <row r="623">
@@ -29155,10 +29155,10 @@
         <v>1.55</v>
       </c>
       <c r="I623" t="n">
-        <v>0.6432</v>
+        <v>0.6434</v>
       </c>
       <c r="J623" t="n">
-        <v>10.2912</v>
+        <v>10.2944</v>
       </c>
     </row>
     <row r="624">
@@ -29195,10 +29195,10 @@
         <v>1.54</v>
       </c>
       <c r="I624" t="n">
-        <v>0.6338</v>
+        <v>0.6339</v>
       </c>
       <c r="J624" t="n">
-        <v>10.1408</v>
+        <v>10.1424</v>
       </c>
     </row>
     <row r="625">
@@ -29232,13 +29232,13 @@
         <v>16</v>
       </c>
       <c r="H625" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="I625" t="n">
-        <v>0.4048</v>
+        <v>0.394</v>
       </c>
       <c r="J625" t="n">
-        <v>6.4768</v>
+        <v>6.304</v>
       </c>
     </row>
     <row r="626">
@@ -29275,10 +29275,10 @@
         <v>1.05</v>
       </c>
       <c r="I626" t="n">
-        <v>0.0697</v>
+        <v>0.0699</v>
       </c>
       <c r="J626" t="n">
-        <v>1.1152</v>
+        <v>1.1184</v>
       </c>
     </row>
     <row r="627">
@@ -29315,10 +29315,10 @@
         <v>0.86</v>
       </c>
       <c r="I627" t="n">
-        <v>-0.1579</v>
+        <v>-0.1587</v>
       </c>
       <c r="J627" t="n">
-        <v>-2.5264</v>
+        <v>-2.5392</v>
       </c>
     </row>
     <row r="628">
@@ -29355,10 +29355,10 @@
         <v>0.75</v>
       </c>
       <c r="I628" t="n">
-        <v>-0.272</v>
+        <v>-0.2725</v>
       </c>
       <c r="J628" t="n">
-        <v>-4.352</v>
+        <v>-4.36</v>
       </c>
     </row>
     <row r="629">
@@ -29395,10 +29395,10 @@
         <v>0.72</v>
       </c>
       <c r="I629" t="n">
-        <v>-0.2999</v>
+        <v>-0.3003</v>
       </c>
       <c r="J629" t="n">
-        <v>-4.7984</v>
+        <v>-4.8048</v>
       </c>
     </row>
     <row r="630">
@@ -29432,13 +29432,13 @@
         <v>16</v>
       </c>
       <c r="H630" t="n">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="I630" t="n">
-        <v>-0.3703</v>
+        <v>-0.353</v>
       </c>
       <c r="J630" t="n">
-        <v>-5.9248</v>
+        <v>-5.648</v>
       </c>
     </row>
     <row r="631">
@@ -29475,10 +29475,10 @@
         <v>0.53</v>
       </c>
       <c r="I631" t="n">
-        <v>-0.4677</v>
+        <v>-0.4682</v>
       </c>
       <c r="J631" t="n">
-        <v>-7.4832</v>
+        <v>-7.4912</v>
       </c>
     </row>
     <row r="632">
@@ -29715,10 +29715,10 @@
         <v>2</v>
       </c>
       <c r="I637" t="n">
-        <v>1.749</v>
+        <v>1.7498</v>
       </c>
       <c r="J637" t="n">
-        <v>38.478</v>
+        <v>38.4956</v>
       </c>
     </row>
     <row r="638">
@@ -29752,13 +29752,13 @@
         <v>22</v>
       </c>
       <c r="H638" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="I638" t="n">
-        <v>0.8322000000000001</v>
+        <v>0.8127</v>
       </c>
       <c r="J638" t="n">
-        <v>18.3084</v>
+        <v>17.8794</v>
       </c>
     </row>
     <row r="639">
@@ -29795,10 +29795,10 @@
         <v>1.33</v>
       </c>
       <c r="I639" t="n">
-        <v>0.8123</v>
+        <v>0.8127</v>
       </c>
       <c r="J639" t="n">
-        <v>17.8706</v>
+        <v>17.8794</v>
       </c>
     </row>
     <row r="640">
@@ -29835,10 +29835,10 @@
         <v>0.73</v>
       </c>
       <c r="I640" t="n">
-        <v>-0.7815</v>
+        <v>-0.7812</v>
       </c>
       <c r="J640" t="n">
-        <v>-17.193</v>
+        <v>-17.1864</v>
       </c>
     </row>
     <row r="641">
@@ -29875,10 +29875,10 @@
         <v>0.62</v>
       </c>
       <c r="I641" t="n">
-        <v>-1.0105</v>
+        <v>-1.0102</v>
       </c>
       <c r="J641" t="n">
-        <v>-22.231</v>
+        <v>-22.2244</v>
       </c>
     </row>
     <row r="642">
@@ -30115,10 +30115,10 @@
         <v>1.32</v>
       </c>
       <c r="I647" t="n">
-        <v>0.6148</v>
+        <v>0.6143</v>
       </c>
       <c r="J647" t="n">
-        <v>13.5256</v>
+        <v>13.5146</v>
       </c>
     </row>
     <row r="648">
@@ -30155,10 +30155,10 @@
         <v>1.13</v>
       </c>
       <c r="I648" t="n">
-        <v>0.3004</v>
+        <v>0.3001</v>
       </c>
       <c r="J648" t="n">
-        <v>6.6088</v>
+        <v>6.6022</v>
       </c>
     </row>
     <row r="649">
@@ -30195,10 +30195,10 @@
         <v>1.12</v>
       </c>
       <c r="I649" t="n">
-        <v>0.282</v>
+        <v>0.2817</v>
       </c>
       <c r="J649" t="n">
-        <v>6.204</v>
+        <v>6.1974</v>
       </c>
     </row>
     <row r="650">
@@ -30232,13 +30232,13 @@
         <v>22</v>
       </c>
       <c r="H650" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="I650" t="n">
-        <v>0.2443</v>
+        <v>0.2631</v>
       </c>
       <c r="J650" t="n">
-        <v>5.3746</v>
+        <v>5.7882</v>
       </c>
     </row>
     <row r="651">
@@ -30275,10 +30275,10 @@
         <v>0.59</v>
       </c>
       <c r="I651" t="n">
-        <v>-0.45</v>
+        <v>-0.4501</v>
       </c>
       <c r="J651" t="n">
-        <v>-9.9</v>
+        <v>-9.902200000000001</v>
       </c>
     </row>
     <row r="652">
@@ -30315,10 +30315,10 @@
         <v>1.07</v>
       </c>
       <c r="I652" t="n">
-        <v>0.1586</v>
+        <v>0.1582</v>
       </c>
       <c r="J652" t="n">
-        <v>4.5994</v>
+        <v>4.5878</v>
       </c>
     </row>
     <row r="653">
@@ -30355,10 +30355,10 @@
         <v>0.97</v>
       </c>
       <c r="I653" t="n">
-        <v>-0.0549</v>
+        <v>-0.055</v>
       </c>
       <c r="J653" t="n">
-        <v>-1.5921</v>
+        <v>-1.595</v>
       </c>
     </row>
     <row r="654">
@@ -30395,10 +30395,10 @@
         <v>0.95</v>
       </c>
       <c r="I654" t="n">
-        <v>-0.0825</v>
+        <v>-0.08260000000000001</v>
       </c>
       <c r="J654" t="n">
-        <v>-2.3925</v>
+        <v>-2.3954</v>
       </c>
     </row>
     <row r="655">
@@ -30432,13 +30432,13 @@
         <v>29</v>
       </c>
       <c r="H655" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="I655" t="n">
-        <v>-0.1421</v>
+        <v>-0.1309</v>
       </c>
       <c r="J655" t="n">
-        <v>-4.1209</v>
+        <v>-3.7961</v>
       </c>
     </row>
     <row r="656">
@@ -30475,10 +30475,10 @@
         <v>0.82</v>
       </c>
       <c r="I656" t="n">
-        <v>-0.227</v>
+        <v>-0.2272</v>
       </c>
       <c r="J656" t="n">
-        <v>-6.583</v>
+        <v>-6.5888</v>
       </c>
     </row>
     <row r="657">
@@ -31915,10 +31915,10 @@
         <v>1.1</v>
       </c>
       <c r="I692" t="n">
-        <v>0.2778</v>
+        <v>0.2772</v>
       </c>
       <c r="J692" t="n">
-        <v>6.1116</v>
+        <v>6.0984</v>
       </c>
     </row>
     <row r="693">
@@ -31955,10 +31955,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I693" t="n">
-        <v>-0.09130000000000001</v>
+        <v>-0.0915</v>
       </c>
       <c r="J693" t="n">
-        <v>-2.0086</v>
+        <v>-2.013</v>
       </c>
     </row>
     <row r="694">
@@ -31995,10 +31995,10 @@
         <v>0.86</v>
       </c>
       <c r="I694" t="n">
-        <v>-0.1813</v>
+        <v>-0.1814</v>
       </c>
       <c r="J694" t="n">
-        <v>-3.9886</v>
+        <v>-3.9908</v>
       </c>
     </row>
     <row r="695">
@@ -32035,10 +32035,10 @@
         <v>0.78</v>
       </c>
       <c r="I695" t="n">
-        <v>-0.2616</v>
+        <v>-0.2618</v>
       </c>
       <c r="J695" t="n">
-        <v>-5.7552</v>
+        <v>-5.7596</v>
       </c>
     </row>
     <row r="696">
@@ -32072,13 +32072,13 @@
         <v>22</v>
       </c>
       <c r="H696" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="I696" t="n">
-        <v>-0.2712</v>
+        <v>-0.2618</v>
       </c>
       <c r="J696" t="n">
-        <v>-5.9664</v>
+        <v>-5.7596</v>
       </c>
     </row>
     <row r="697">
@@ -32115,10 +32115,10 @@
         <v>1.42</v>
       </c>
       <c r="I697" t="n">
-        <v>0.9903</v>
+        <v>0.9908</v>
       </c>
       <c r="J697" t="n">
-        <v>21.7866</v>
+        <v>21.7976</v>
       </c>
     </row>
     <row r="698">
@@ -32152,13 +32152,13 @@
         <v>22</v>
       </c>
       <c r="H698" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="I698" t="n">
-        <v>0.5043</v>
+        <v>0.4826</v>
       </c>
       <c r="J698" t="n">
-        <v>11.0946</v>
+        <v>10.6172</v>
       </c>
     </row>
     <row r="699">
@@ -32195,10 +32195,10 @@
         <v>1.17</v>
       </c>
       <c r="I699" t="n">
-        <v>0.4824</v>
+        <v>0.4826</v>
       </c>
       <c r="J699" t="n">
-        <v>10.6128</v>
+        <v>10.6172</v>
       </c>
     </row>
     <row r="700">
@@ -32235,10 +32235,10 @@
         <v>1.08</v>
       </c>
       <c r="I700" t="n">
-        <v>0.261</v>
+        <v>0.2613</v>
       </c>
       <c r="J700" t="n">
-        <v>5.742</v>
+        <v>5.7486</v>
       </c>
     </row>
     <row r="701">
@@ -32275,10 +32275,10 @@
         <v>1.02</v>
       </c>
       <c r="I701" t="n">
-        <v>0.0722</v>
+        <v>0.0725</v>
       </c>
       <c r="J701" t="n">
-        <v>1.5884</v>
+        <v>1.595</v>
       </c>
     </row>
     <row r="702">
@@ -32915,10 +32915,10 @@
         <v>1.76</v>
       </c>
       <c r="I717" t="n">
-        <v>1.4354</v>
+        <v>1.4359</v>
       </c>
       <c r="J717" t="n">
-        <v>31.5788</v>
+        <v>31.5898</v>
       </c>
     </row>
     <row r="718">
@@ -32952,13 +32952,13 @@
         <v>22</v>
       </c>
       <c r="H718" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="I718" t="n">
-        <v>1.1485</v>
+        <v>1.1355</v>
       </c>
       <c r="J718" t="n">
-        <v>25.267</v>
+        <v>24.981</v>
       </c>
     </row>
     <row r="719">
@@ -32995,10 +32995,10 @@
         <v>1.12</v>
       </c>
       <c r="I719" t="n">
-        <v>0.3535</v>
+        <v>0.3539</v>
       </c>
       <c r="J719" t="n">
-        <v>7.777</v>
+        <v>7.7858</v>
       </c>
     </row>
     <row r="720">
@@ -33035,10 +33035,10 @@
         <v>1.03</v>
       </c>
       <c r="I720" t="n">
-        <v>0.0959</v>
+        <v>0.0963</v>
       </c>
       <c r="J720" t="n">
-        <v>2.1098</v>
+        <v>2.1186</v>
       </c>
     </row>
     <row r="721">
@@ -33075,10 +33075,10 @@
         <v>0.79</v>
       </c>
       <c r="I721" t="n">
-        <v>-0.656</v>
+        <v>-0.6556</v>
       </c>
       <c r="J721" t="n">
-        <v>-14.432</v>
+        <v>-14.4232</v>
       </c>
     </row>
     <row r="722">
@@ -34315,10 +34315,10 @@
         <v>2.13</v>
       </c>
       <c r="I752" t="n">
-        <v>1.9117</v>
+        <v>1.9109</v>
       </c>
       <c r="J752" t="n">
-        <v>42.0574</v>
+        <v>42.0398</v>
       </c>
     </row>
     <row r="753">
@@ -34352,13 +34352,13 @@
         <v>22</v>
       </c>
       <c r="H753" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="I753" t="n">
-        <v>0.6094000000000001</v>
+        <v>0.6301</v>
       </c>
       <c r="J753" t="n">
-        <v>13.4068</v>
+        <v>13.8622</v>
       </c>
     </row>
     <row r="754">
@@ -34395,10 +34395,10 @@
         <v>1.21</v>
       </c>
       <c r="I754" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.5667</v>
       </c>
       <c r="J754" t="n">
-        <v>12.474</v>
+        <v>12.4674</v>
       </c>
     </row>
     <row r="755">
@@ -34435,10 +34435,10 @@
         <v>0.85</v>
       </c>
       <c r="I755" t="n">
-        <v>-0.5062</v>
+        <v>-0.5065</v>
       </c>
       <c r="J755" t="n">
-        <v>-11.1364</v>
+        <v>-11.143</v>
       </c>
     </row>
     <row r="756">
@@ -34475,10 +34475,10 @@
         <v>0.55</v>
       </c>
       <c r="I756" t="n">
-        <v>-1.148</v>
+        <v>-1.1482</v>
       </c>
       <c r="J756" t="n">
-        <v>-25.256</v>
+        <v>-25.2604</v>
       </c>
     </row>
     <row r="757">
@@ -34715,10 +34715,10 @@
         <v>1.25</v>
       </c>
       <c r="I762" t="n">
-        <v>0.4416</v>
+        <v>0.439</v>
       </c>
       <c r="J762" t="n">
-        <v>9.715199999999999</v>
+        <v>9.657999999999999</v>
       </c>
     </row>
     <row r="763">
@@ -34752,13 +34752,13 @@
         <v>22</v>
       </c>
       <c r="H763" t="n">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="I763" t="n">
-        <v>-0.0459</v>
+        <v>-0.031</v>
       </c>
       <c r="J763" t="n">
-        <v>-1.0098</v>
+        <v>-0.6820000000000001</v>
       </c>
     </row>
     <row r="764">
@@ -34792,13 +34792,13 @@
         <v>22</v>
       </c>
       <c r="H764" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="I764" t="n">
-        <v>-0.1584</v>
+        <v>-0.1482</v>
       </c>
       <c r="J764" t="n">
-        <v>-3.4848</v>
+        <v>-3.2604</v>
       </c>
     </row>
     <row r="765">
@@ -34832,13 +34832,13 @@
         <v>22</v>
       </c>
       <c r="H765" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="I765" t="n">
-        <v>-0.4064</v>
+        <v>-0.3983</v>
       </c>
       <c r="J765" t="n">
-        <v>-8.940799999999999</v>
+        <v>-8.762600000000001</v>
       </c>
     </row>
     <row r="766">
@@ -34872,13 +34872,13 @@
         <v>22</v>
       </c>
       <c r="H766" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="I766" t="n">
-        <v>-0.4506</v>
+        <v>-0.4426</v>
       </c>
       <c r="J766" t="n">
-        <v>-9.9132</v>
+        <v>-9.7372</v>
       </c>
     </row>
     <row r="767">
@@ -34912,13 +34912,13 @@
         <v>22</v>
       </c>
       <c r="H767" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="I767" t="n">
-        <v>0.8514</v>
+        <v>0.8351</v>
       </c>
       <c r="J767" t="n">
-        <v>18.7308</v>
+        <v>18.3722</v>
       </c>
     </row>
     <row r="768">
@@ -34952,13 +34952,13 @@
         <v>22</v>
       </c>
       <c r="H768" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="I768" t="n">
-        <v>0.6701</v>
+        <v>0.6425</v>
       </c>
       <c r="J768" t="n">
-        <v>14.7422</v>
+        <v>14.135</v>
       </c>
     </row>
     <row r="769">
@@ -34992,13 +34992,13 @@
         <v>22</v>
       </c>
       <c r="H769" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="I769" t="n">
-        <v>0.4263</v>
+        <v>0.4378</v>
       </c>
       <c r="J769" t="n">
-        <v>9.3786</v>
+        <v>9.631600000000001</v>
       </c>
     </row>
     <row r="770">
@@ -35032,13 +35032,13 @@
         <v>22</v>
       </c>
       <c r="H770" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="I770" t="n">
-        <v>0.1316</v>
+        <v>0.1015</v>
       </c>
       <c r="J770" t="n">
-        <v>2.8952</v>
+        <v>2.233</v>
       </c>
     </row>
     <row r="771">
@@ -35072,13 +35072,13 @@
         <v>22</v>
       </c>
       <c r="H771" t="n">
-        <v>0.8</v>
+        <v>0.79</v>
       </c>
       <c r="I771" t="n">
-        <v>-0.2756</v>
+        <v>-0.2845</v>
       </c>
       <c r="J771" t="n">
-        <v>-6.0632</v>
+        <v>-6.259</v>
       </c>
     </row>
     <row r="772">
@@ -35592,13 +35592,13 @@
         <v>23</v>
       </c>
       <c r="H784" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="I784" t="n">
-        <v>0.7119</v>
+        <v>0.7323</v>
       </c>
       <c r="J784" t="n">
-        <v>16.3737</v>
+        <v>16.8429</v>
       </c>
     </row>
     <row r="785">
@@ -35632,13 +35632,13 @@
         <v>23</v>
       </c>
       <c r="H785" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="I785" t="n">
-        <v>0.6501</v>
+        <v>0.6293</v>
       </c>
       <c r="J785" t="n">
-        <v>14.9523</v>
+        <v>14.4739</v>
       </c>
     </row>
     <row r="786">
@@ -35715,10 +35715,10 @@
         <v>1.36</v>
       </c>
       <c r="I787" t="n">
-        <v>0.7030999999999999</v>
+        <v>0.7024</v>
       </c>
       <c r="J787" t="n">
-        <v>16.1713</v>
+        <v>16.1552</v>
       </c>
     </row>
     <row r="788">
@@ -35755,10 +35755,10 @@
         <v>1.32</v>
       </c>
       <c r="I788" t="n">
-        <v>0.6405</v>
+        <v>0.6399</v>
       </c>
       <c r="J788" t="n">
-        <v>14.7315</v>
+        <v>14.7177</v>
       </c>
     </row>
     <row r="789">
@@ -35792,13 +35792,13 @@
         <v>23</v>
       </c>
       <c r="H789" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="I789" t="n">
-        <v>-0.166</v>
+        <v>-0.1551</v>
       </c>
       <c r="J789" t="n">
-        <v>-3.818</v>
+        <v>-3.5673</v>
       </c>
     </row>
     <row r="790">
@@ -35835,10 +35835,10 @@
         <v>0.82</v>
       </c>
       <c r="I790" t="n">
-        <v>-0.2289</v>
+        <v>-0.2291</v>
       </c>
       <c r="J790" t="n">
-        <v>-5.2647</v>
+        <v>-5.2693</v>
       </c>
     </row>
     <row r="791">
@@ -35875,10 +35875,10 @@
         <v>0.43</v>
       </c>
       <c r="I791" t="n">
-        <v>-0.5787</v>
+        <v>-0.5789</v>
       </c>
       <c r="J791" t="n">
-        <v>-13.3101</v>
+        <v>-13.3147</v>
       </c>
     </row>
     <row r="792">
@@ -36715,10 +36715,10 @@
         <v>1.4</v>
       </c>
       <c r="I812" t="n">
-        <v>0.9517</v>
+        <v>0.9522</v>
       </c>
       <c r="J812" t="n">
-        <v>19.9857</v>
+        <v>19.9962</v>
       </c>
     </row>
     <row r="813">
@@ -36755,10 +36755,10 @@
         <v>1.33</v>
       </c>
       <c r="I813" t="n">
-        <v>0.8157</v>
+        <v>0.8162</v>
       </c>
       <c r="J813" t="n">
-        <v>17.1297</v>
+        <v>17.1402</v>
       </c>
     </row>
     <row r="814">
@@ -36795,10 +36795,10 @@
         <v>1.22</v>
       </c>
       <c r="I814" t="n">
-        <v>0.589</v>
+        <v>0.5893</v>
       </c>
       <c r="J814" t="n">
-        <v>12.369</v>
+        <v>12.3753</v>
       </c>
     </row>
     <row r="815">
@@ -36835,10 +36835,10 @@
         <v>1.08</v>
       </c>
       <c r="I815" t="n">
-        <v>0.2587</v>
+        <v>0.259</v>
       </c>
       <c r="J815" t="n">
-        <v>5.4327</v>
+        <v>5.439</v>
       </c>
     </row>
     <row r="816">
@@ -36872,13 +36872,13 @@
         <v>21</v>
       </c>
       <c r="H816" t="n">
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
       <c r="I816" t="n">
-        <v>-0.351</v>
+        <v>-0.3777</v>
       </c>
       <c r="J816" t="n">
-        <v>-7.371</v>
+        <v>-7.9317</v>
       </c>
     </row>
     <row r="817">
@@ -39515,10 +39515,10 @@
         <v>1.72</v>
       </c>
       <c r="I882" t="n">
-        <v>1.3596</v>
+        <v>1.36</v>
       </c>
       <c r="J882" t="n">
-        <v>23.1132</v>
+        <v>23.12</v>
       </c>
     </row>
     <row r="883">
@@ -39555,10 +39555,10 @@
         <v>1.61</v>
       </c>
       <c r="I883" t="n">
-        <v>1.2202</v>
+        <v>1.2205</v>
       </c>
       <c r="J883" t="n">
-        <v>20.7434</v>
+        <v>20.7485</v>
       </c>
     </row>
     <row r="884">
@@ -39595,10 +39595,10 @@
         <v>1.22</v>
       </c>
       <c r="I884" t="n">
-        <v>0.5676</v>
+        <v>0.5679</v>
       </c>
       <c r="J884" t="n">
-        <v>9.6492</v>
+        <v>9.654299999999999</v>
       </c>
     </row>
     <row r="885">
@@ -39635,10 +39635,10 @@
         <v>1.17</v>
       </c>
       <c r="I885" t="n">
-        <v>0.4561</v>
+        <v>0.4564</v>
       </c>
       <c r="J885" t="n">
-        <v>7.7537</v>
+        <v>7.7588</v>
       </c>
     </row>
     <row r="886">
@@ -39672,13 +39672,13 @@
         <v>17</v>
       </c>
       <c r="H886" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="I886" t="n">
-        <v>0.2028</v>
+        <v>0.174</v>
       </c>
       <c r="J886" t="n">
-        <v>3.4476</v>
+        <v>2.958</v>
       </c>
     </row>
     <row r="887">
@@ -39715,10 +39715,10 @@
         <v>1.07</v>
       </c>
       <c r="I887" t="n">
-        <v>0.2464</v>
+        <v>0.2456</v>
       </c>
       <c r="J887" t="n">
-        <v>4.1888</v>
+        <v>4.1752</v>
       </c>
     </row>
     <row r="888">
@@ -39752,13 +39752,13 @@
         <v>17</v>
       </c>
       <c r="H888" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="I888" t="n">
-        <v>-0.1622</v>
+        <v>-0.1514</v>
       </c>
       <c r="J888" t="n">
-        <v>-2.7574</v>
+        <v>-2.5738</v>
       </c>
     </row>
     <row r="889">
@@ -39795,10 +39795,10 @@
         <v>0.84</v>
       </c>
       <c r="I889" t="n">
-        <v>-0.1942</v>
+        <v>-0.1944</v>
       </c>
       <c r="J889" t="n">
-        <v>-3.3014</v>
+        <v>-3.3048</v>
       </c>
     </row>
     <row r="890">
@@ -39835,10 +39835,10 @@
         <v>0.63</v>
       </c>
       <c r="I890" t="n">
-        <v>-0.3902</v>
+        <v>-0.3904</v>
       </c>
       <c r="J890" t="n">
-        <v>-6.6334</v>
+        <v>-6.6368</v>
       </c>
     </row>
     <row r="891">
@@ -39875,10 +39875,10 @@
         <v>0.55</v>
       </c>
       <c r="I891" t="n">
-        <v>-0.4612</v>
+        <v>-0.4614</v>
       </c>
       <c r="J891" t="n">
-        <v>-7.8404</v>
+        <v>-7.8438</v>
       </c>
     </row>
     <row r="892">
@@ -40192,13 +40192,13 @@
         <v>20</v>
       </c>
       <c r="H899" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="I899" t="n">
-        <v>-0.1167</v>
+        <v>-0.1047</v>
       </c>
       <c r="J899" t="n">
-        <v>-2.334</v>
+        <v>-2.094</v>
       </c>
     </row>
     <row r="900">
@@ -40232,13 +40232,13 @@
         <v>20</v>
       </c>
       <c r="H900" t="n">
-        <v>0.85</v>
+        <v>0.84</v>
       </c>
       <c r="I900" t="n">
-        <v>-0.1925</v>
+        <v>-0.2028</v>
       </c>
       <c r="J900" t="n">
-        <v>-3.85</v>
+        <v>-4.056</v>
       </c>
     </row>
     <row r="901">
@@ -40315,10 +40315,10 @@
         <v>2.16</v>
       </c>
       <c r="I902" t="n">
-        <v>1.8861</v>
+        <v>1.8867</v>
       </c>
       <c r="J902" t="n">
-        <v>32.0637</v>
+        <v>32.0739</v>
       </c>
     </row>
     <row r="903">
@@ -40355,10 +40355,10 @@
         <v>1.51</v>
       </c>
       <c r="I903" t="n">
-        <v>1.0886</v>
+        <v>1.0889</v>
       </c>
       <c r="J903" t="n">
-        <v>18.5062</v>
+        <v>18.5113</v>
       </c>
     </row>
     <row r="904">
@@ -40392,13 +40392,13 @@
         <v>17</v>
       </c>
       <c r="H904" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="I904" t="n">
-        <v>0.4077</v>
+        <v>0.3841</v>
       </c>
       <c r="J904" t="n">
-        <v>6.9309</v>
+        <v>6.5297</v>
       </c>
     </row>
     <row r="905">
@@ -40435,10 +40435,10 @@
         <v>1.13</v>
       </c>
       <c r="I905" t="n">
-        <v>0.3593</v>
+        <v>0.3597</v>
       </c>
       <c r="J905" t="n">
-        <v>6.1081</v>
+        <v>6.1149</v>
       </c>
     </row>
     <row r="906">
@@ -40475,10 +40475,10 @@
         <v>0.89</v>
       </c>
       <c r="I906" t="n">
-        <v>-0.4333</v>
+        <v>-0.433</v>
       </c>
       <c r="J906" t="n">
-        <v>-7.3661</v>
+        <v>-7.361</v>
       </c>
     </row>
     <row r="907">
@@ -40515,10 +40515,10 @@
         <v>1.58</v>
       </c>
       <c r="I907" t="n">
-        <v>1.0624</v>
+        <v>1.0614</v>
       </c>
       <c r="J907" t="n">
-        <v>18.0608</v>
+        <v>18.0438</v>
       </c>
     </row>
     <row r="908">
@@ -40555,10 +40555,10 @@
         <v>0.91</v>
       </c>
       <c r="I908" t="n">
-        <v>-0.1247</v>
+        <v>-0.1249</v>
       </c>
       <c r="J908" t="n">
-        <v>-2.1199</v>
+        <v>-2.1233</v>
       </c>
     </row>
     <row r="909">
@@ -40592,13 +40592,13 @@
         <v>17</v>
       </c>
       <c r="H909" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="I909" t="n">
-        <v>-0.3059</v>
+        <v>-0.2968</v>
       </c>
       <c r="J909" t="n">
-        <v>-5.2003</v>
+        <v>-5.0456</v>
       </c>
     </row>
     <row r="910">
@@ -40635,10 +40635,10 @@
         <v>0.63</v>
       </c>
       <c r="I910" t="n">
-        <v>-0.3975</v>
+        <v>-0.3977</v>
       </c>
       <c r="J910" t="n">
-        <v>-6.7575</v>
+        <v>-6.7609</v>
       </c>
     </row>
     <row r="911">
@@ -40675,10 +40675,10 @@
         <v>0.44</v>
       </c>
       <c r="I911" t="n">
-        <v>-0.5624</v>
+        <v>-0.5626</v>
       </c>
       <c r="J911" t="n">
-        <v>-9.5608</v>
+        <v>-9.5642</v>
       </c>
     </row>
     <row r="912">
@@ -41115,10 +41115,10 @@
         <v>1.82</v>
       </c>
       <c r="I922" t="n">
-        <v>1.53</v>
+        <v>1.5306</v>
       </c>
       <c r="J922" t="n">
-        <v>33.66</v>
+        <v>33.6732</v>
       </c>
     </row>
     <row r="923">
@@ -41155,10 +41155,10 @@
         <v>1.38</v>
       </c>
       <c r="I923" t="n">
-        <v>0.9147</v>
+        <v>0.9152</v>
       </c>
       <c r="J923" t="n">
-        <v>20.1234</v>
+        <v>20.1344</v>
       </c>
     </row>
     <row r="924">
@@ -41195,10 +41195,10 @@
         <v>1.15</v>
       </c>
       <c r="I924" t="n">
-        <v>0.4355</v>
+        <v>0.4358</v>
       </c>
       <c r="J924" t="n">
-        <v>9.581</v>
+        <v>9.5876</v>
       </c>
     </row>
     <row r="925">
@@ -41232,13 +41232,13 @@
         <v>22</v>
       </c>
       <c r="H925" t="n">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="I925" t="n">
-        <v>-0.529</v>
+        <v>-0.5526</v>
       </c>
       <c r="J925" t="n">
-        <v>-11.638</v>
+        <v>-12.1572</v>
       </c>
     </row>
     <row r="926">
@@ -41275,10 +41275,10 @@
         <v>0.74</v>
       </c>
       <c r="I926" t="n">
-        <v>-0.757</v>
+        <v>-0.7566000000000001</v>
       </c>
       <c r="J926" t="n">
-        <v>-16.654</v>
+        <v>-16.6452</v>
       </c>
     </row>
     <row r="927">
